--- a/promotions_extraites.xlsx
+++ b/promotions_extraites.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Promotions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Promotions'!$A$1:$Q$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Promotions'!$A$1:$Q$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q202"/>
+  <dimension ref="A1:Q259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3472,11 +3472,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3601,11 +3601,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3645,11 +3645,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4092,11 +4092,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Haribo Pixels acidulés, 1,2 kg</t>
+          <t>BrokenTaco Diablo Crema, Sweet Taco Topping ou Green Sriracha, 200 g</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -4104,18 +4104,13 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Hit</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="n"/>
-      <c r="O79" s="2" t="n">
-        <v>9.5</v>
-      </c>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O79" s="2" t="n"/>
       <c r="P79" s="2" t="n"/>
       <c r="Q79" s="3" t="n"/>
     </row>
@@ -4130,44 +4125,28 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Olives en sachet Migros (excepté Demeter et Alnatura) (p. ex. olives espagnoles Hojiblanca dénoyautées, 150 g)</t>
+          <t>Haribo Pixels acidulés, 1,2 kg</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Espagne</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>à partir de 2 articles</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>2.7</v>
-      </c>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n"/>
       <c r="O80" s="2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P80" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q80" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>9.5</v>
+      </c>
+      <c r="P80" s="2" t="n"/>
+      <c r="Q80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4180,7 +4159,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croissants au jambon Happy Hour, M-Classic, surgelé, 24 pièces, 1008 g</t>
+          <t>Olives en sachet Migros (excepté Demeter et Alnatura) (p. ex. olives espagnoles Hojiblanca dénoyautées, 150 g)</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -4191,22 +4170,32 @@
           <t>7.2</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Espagne</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>à partir de 2 articles</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>20%</t>
         </is>
       </c>
       <c r="N81" s="2" t="n">
-        <v>12.6</v>
+        <v>2.7</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>2.16</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>3.8</v>
+        <v>0.54</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>30.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
@@ -4220,7 +4209,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pepsi, Regular, Zero, Cherry Zero et sans caféine (p. ex. Regular, 6 x 1,5 litre)</t>
+          <t>Croissants au jambon Happy Hour, M-Classic, surgelé, 24 pièces, 1008 g</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -4228,30 +4217,25 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>pack de 6</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>40%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="N82" s="2" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>40</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="83">
@@ -4265,7 +4249,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Biscuits pour l'apéritif Party, Pizza Crackers, Crackers ou Sticks (p. ex. pizza crackers, 450 g)</t>
+          <t>Pepsi, Regular, Zero, Cherry Zero et sans caféine (p. ex. Regular, 6 x 1,5 litre)</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -4273,25 +4257,30 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>pack de 6</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
       <c r="N83" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>20.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84">
@@ -4305,20 +4294,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Salsiccia Ticinese Rapelli, 480 g</t>
+          <t>Biscuits pour l'apéritif Party, Pizza Crackers, Crackers ou Sticks (p. ex. pizza crackers, 450 g)</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Suisse</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4327,16 +4311,16 @@
         </is>
       </c>
       <c r="N84" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>7.95</v>
+        <v>7.4</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="85">
@@ -4350,38 +4334,38 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chips Zweifel, paprika ou nature, 2 x 175 g</t>
+          <t>Salsiccia Ticinese Rapelli, 480 g</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Suisse</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>lot de 2</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>23%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="N85" s="2" t="n">
-        <v>8.4</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O85" s="2" t="n">
-        <v>6.45</v>
+        <v>7.95</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>23.2</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="86">
@@ -4395,7 +4379,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Snacketti Zweifel, Paprika Shells, Dancer Cream ou Bacon Strips Flavour, XXL Big Pack, 225 g</t>
+          <t>Chips Zweifel, paprika ou nature, 2 x 175 g</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -4408,20 +4392,25 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>lot de 2</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>23%</t>
         </is>
       </c>
       <c r="N86" s="2" t="n">
-        <v>5.85</v>
+        <v>8.4</v>
       </c>
       <c r="O86" s="2" t="n">
-        <v>4.65</v>
+        <v>6.45</v>
       </c>
       <c r="P86" s="2" t="n">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>20.5</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="87">
@@ -4431,42 +4420,37 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Eau minérale Aproz, diverses variétés (p. ex. gazéifiée, 6 x 1,5 litre)</t>
+          <t>Snacketti Zweifel, Paprika Shells, Dancer Cream ou Bacon Strips Flavour, XXL Big Pack, 225 g</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>pack de 6</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="N87" s="2" t="n">
-        <v>6.4</v>
+        <v>5.85</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q87" s="3" t="n">
-        <v>50</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="88">
@@ -4480,15 +4464,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Schweppes, diverses variétés (p. ex. Bitter Lemon, 6 x 500 ml)</t>
+          <t>Eau minérale Aproz, diverses variétés (p. ex. gazéifiée, 6 x 1,5 litre)</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4498,20 +4482,20 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="N88" s="2" t="n">
-        <v>11.9</v>
+        <v>6.4</v>
       </c>
       <c r="O88" s="2" t="n">
-        <v>7.14</v>
+        <v>3.2</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>4.76</v>
+        <v>3.2</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -4525,7 +4509,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Red Bull Sugarfree ou Zero, 6 x 250 ml</t>
+          <t>Schweppes, diverses variétés (p. ex. Bitter Lemon, 6 x 500 ml)</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -4543,20 +4527,20 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="N89" s="2" t="n">
-        <v>8.9</v>
+        <v>11.9</v>
       </c>
       <c r="O89" s="2" t="n">
-        <v>6.05</v>
+        <v>7.14</v>
       </c>
       <c r="P89" s="2" t="n">
-        <v>2.85</v>
+        <v>4.76</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -4570,7 +4554,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Capri-Sun Multivitamin, Multivitamin Zero, Monster ou Mystic Dragon, 10 x 200 ml</t>
+          <t>Red Bull Sugarfree ou Zero, 6 x 250 ml</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4583,25 +4567,25 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>pack de 10</t>
+          <t>pack de 6</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="N90" s="2" t="n">
-        <v>4.95</v>
+        <v>8.9</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>3.3</v>
+        <v>6.05</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>1.65</v>
+        <v>2.85</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>33.3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
@@ -4615,7 +4599,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tous les sirops en bouteilles PET (p. ex. framboise, 750 ml)</t>
+          <t>Capri-Sun Multivitamin, Multivitamin Zero, Monster ou Mystic Dragon, 10 x 200 ml</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4628,20 +4612,25 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>pack de 10</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>33%</t>
         </is>
       </c>
       <c r="N91" s="2" t="n">
-        <v>2.95</v>
+        <v>4.95</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>0.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="92">
@@ -4655,7 +4644,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Red Bull Summer Edition Sugarfree Sudachi-Lime, 250 ml</t>
+          <t>Tous les sirops en bouteilles PET (p. ex. framboise, 750 ml)</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4668,20 +4657,21 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Nouveau</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>20x Cumulus</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="n"/>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>2.95</v>
+      </c>
       <c r="O92" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P92" s="2" t="n"/>
-      <c r="Q92" s="3" t="n"/>
+        <v>2.36</v>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Q92" s="3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4694,15 +4684,15 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Volvic Essence agrumes-romarin (p. ex. 6 x 750 ml)</t>
+          <t>Red Bull Summer Edition Sugarfree Sudachi-Lime, 250 ml</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4717,7 +4707,7 @@
       </c>
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="2" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="P93" s="2" t="n"/>
       <c r="Q93" s="3" t="n"/>
@@ -4733,7 +4723,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Eau minérale Evian Sparkling, 500 ml</t>
+          <t>Volvic Essence agrumes-romarin (p. ex. 6 x 750 ml)</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4741,7 +4731,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -4756,7 +4746,7 @@
       </c>
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="2" t="n">
-        <v>1.1</v>
+        <v>11.7</v>
       </c>
       <c r="P94" s="2" t="n"/>
       <c r="Q94" s="3" t="n"/>
@@ -4768,19 +4758,19 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lillet Blanc, sans alcool, 750 ml</t>
+          <t>Eau minérale Evian Sparkling, 500 ml</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -4795,7 +4785,7 @@
       </c>
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="2" t="n">
-        <v>19.95</v>
+        <v>1.1</v>
       </c>
       <c r="P95" s="2" t="n"/>
       <c r="Q95" s="3" t="n"/>
@@ -4811,7 +4801,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Monster Bad Apple Energy et Juice, 500 ml</t>
+          <t>Lillet Blanc, sans alcool, 750 ml</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -4834,7 +4824,7 @@
       </c>
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="2" t="n">
-        <v>1.7</v>
+        <v>19.95</v>
       </c>
       <c r="P96" s="2" t="n"/>
       <c r="Q96" s="3" t="n"/>
@@ -4850,7 +4840,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lamate Mango Migros, 330 ml</t>
+          <t>Monster Bad Apple Energy et Juice, 500 ml</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4873,7 +4863,7 @@
       </c>
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="2" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="3" t="n"/>
@@ -4889,7 +4879,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fanta Orange (p. ex. 6 x 330 ml)</t>
+          <t>Lamate Mango Migros, 330 ml</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4912,7 +4902,7 @@
       </c>
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="2" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="P98" s="2" t="n"/>
       <c r="Q98" s="3" t="n"/>
@@ -4928,7 +4918,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spezi Paulaner, 330 ml</t>
+          <t>Fanta Orange (p. ex. 6 x 330 ml)</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4951,7 +4941,7 @@
       </c>
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="2" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="P99" s="2" t="n"/>
       <c r="Q99" s="3" t="n"/>
@@ -4967,7 +4957,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Freixenet Solare, 750 ml</t>
+          <t>Spezi Paulaner, 330 ml</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4975,7 +4965,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4990,7 +4980,7 @@
       </c>
       <c r="N100" s="2" t="n"/>
       <c r="O100" s="2" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="P100" s="2" t="n"/>
       <c r="Q100" s="3" t="n"/>
@@ -5006,7 +4996,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bilz Chill &amp; Relax, sans alcool, White Peach &amp; Jasmine, 6 x 330 ml</t>
+          <t>Freixenet Solare, 750 ml</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -5014,7 +5004,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5029,7 +5019,7 @@
       </c>
       <c r="N101" s="2" t="n"/>
       <c r="O101" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="P101" s="2" t="n"/>
       <c r="Q101" s="3" t="n"/>
@@ -5045,20 +5035,15 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Biotta Well Fibres bio, 500 ml</t>
+          <t>Bilz Chill &amp; Relax, sans alcool, White Peach &amp; Jasmine, 6 x 330 ml</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bio</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5073,7 +5058,7 @@
       </c>
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="2" t="n">
-        <v>4.95</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="P102" s="2" t="n"/>
       <c r="Q102" s="3" t="n"/>
@@ -5089,15 +5074,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Coca-Cola zéro caféine et zéro sucre (p. ex. 1,5 litre)</t>
+          <t>Biotta Well Fibres bio, 500 ml</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bio</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -5112,7 +5102,7 @@
       </c>
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="2" t="n">
-        <v>14.35</v>
+        <v>4.95</v>
       </c>
       <c r="P103" s="2" t="n"/>
       <c r="Q103" s="3" t="n"/>
@@ -5128,7 +5118,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Matcha Carpe Diem, 500 ml</t>
+          <t>Coca-Cola zéro caféine et zéro sucre (p. ex. 1,5 litre)</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -5151,7 +5141,7 @@
       </c>
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="2" t="n">
-        <v>1.9</v>
+        <v>14.35</v>
       </c>
       <c r="P104" s="2" t="n"/>
       <c r="Q104" s="3" t="n"/>
@@ -5163,43 +5153,37 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Huile de tournesol M-Classic, 1 litre</t>
+          <t>Matcha Carpe Diem, 500 ml</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>à partir de 2 articles</t>
+          <t>Nouveau</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>4</v>
-      </c>
+          <t>20x Cumulus</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="n"/>
       <c r="O105" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q105" s="3" t="n">
-        <v>25</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="P105" s="2" t="n"/>
+      <c r="Q105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5212,48 +5196,38 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pâtes Migros Bio, réfrigérées, tortelloni ricotta e spinaci ou fettuccine aux œufs (p. ex. tortelloni, 3 x 250 g)</t>
+          <t>Huile de tournesol M-Classic, 1 litre</t>
         </is>
       </c>
       <c r="D106" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>à partir de 2 articles</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Migros Bio</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>V-Label végétarien</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>lot de 3</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O106" s="2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="P106" s="2" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107">
@@ -5267,7 +5241,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pizzas au four à bois Anna's Best, réfrigérées, mini Prosciutto ou Prosciutto &amp; mascarpone (p. ex. mini Prosciutto, 3 x 210 g)</t>
+          <t>Pâtes Migros Bio, réfrigérées, tortelloni ricotta e spinaci ou fettuccine aux œufs (p. ex. tortelloni, 3 x 250 g)</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -5278,6 +5252,16 @@
           <t>3.5</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Migros Bio</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>V-Label végétarien</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>lot de 3</t>
@@ -5285,20 +5269,20 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="N107" s="2" t="n">
-        <v>11.85</v>
+        <v>10.5</v>
       </c>
       <c r="O107" s="2" t="n">
-        <v>8.85</v>
+        <v>8.4</v>
       </c>
       <c r="P107" s="2" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>25.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108">
@@ -5312,7 +5296,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Miel de fleurs Fairtrade, crémeux ou liquide (p. ex. crémeux, 2 x 550 g)</t>
+          <t>Pizzas au four à bois Anna's Best, réfrigérées, mini Prosciutto ou Prosciutto &amp; mascarpone (p. ex. mini Prosciutto, 3 x 210 g)</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -5320,35 +5304,30 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Fairtrade Max Havelaar</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>lot de 2</t>
+          <t>lot de 3</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="N108" s="2" t="n">
-        <v>13.9</v>
+        <v>11.85</v>
       </c>
       <c r="O108" s="2" t="n">
-        <v>11.1</v>
+        <v>8.85</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>20.1</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="109">
@@ -5362,38 +5341,43 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tomates concassées Longobardi, 6 x 400 g</t>
+          <t>Miel de fleurs Fairtrade, crémeux ou liquide (p. ex. crémeux, 2 x 550 g)</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Fairtrade Max Havelaar</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>lot de 6</t>
+          <t>lot de 2</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="N109" s="2" t="n">
-        <v>9</v>
+        <v>13.9</v>
       </c>
       <c r="O109" s="2" t="n">
-        <v>6.3</v>
+        <v>11.1</v>
       </c>
       <c r="P109" s="2" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q109" s="3" t="n">
-        <v>30</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="110">
@@ -5407,7 +5391,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tranches d'ananas Sun Queen, lot de 6 (p. ex. 6 x 140 g)</t>
+          <t>Tomates concassées Longobardi, 6 x 400 g</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -5415,12 +5399,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Rainforest Alliance</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5430,20 +5409,20 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="N110" s="2" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>22.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111">
@@ -5457,33 +5436,43 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Crunchy Cream Ovomaltine, 860 g</t>
+          <t>Tranches d'ananas Sun Queen, lot de 6 (p. ex. 6 x 140 g)</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>lot de 6</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>22%</t>
         </is>
       </c>
       <c r="N111" s="2" t="n">
-        <v>10.54</v>
+        <v>7.7</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>2.64</v>
+        <v>1.7</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>25</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="112">
@@ -5497,28 +5486,34 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Riz long grain parboiled Migros, 1 kg</t>
+          <t>Crunchy Cream Ovomaltine, 860 g</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Prix bas</t>
-        </is>
-      </c>
-      <c r="N112" s="2" t="n"/>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>10.54</v>
+      </c>
       <c r="O112" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P112" s="2" t="n"/>
-      <c r="Q112" s="3" t="n"/>
+        <v>7.9</v>
+      </c>
+      <c r="P112" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q112" s="3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5531,7 +5526,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pizzas La Trattoria, surgelées, mozzarella, prosciutto ou tonno (p. ex. mozzarella, 3 x 330 g)</t>
+          <t>Riz long grain parboiled Migros, 1 kg</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5539,31 +5534,20 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>lot de 3</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>5.25</v>
-      </c>
+          <t>Prix bas</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="n"/>
       <c r="O113" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P113" s="2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Q113" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>1.35</v>
+      </c>
+      <c r="P113" s="2" t="n"/>
+      <c r="Q113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5576,20 +5560,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tous les müeslis Farmer (p. ex. baies des bois Classic, 500 g)</t>
+          <t>Pizzas La Trattoria, surgelées, mozzarella, prosciutto ou tonno (p. ex. mozzarella, 3 x 330 g)</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>à partir de 2 articles</t>
+          <t>lot de 3</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -5598,13 +5582,13 @@
         </is>
       </c>
       <c r="N114" s="2" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="O114" s="2" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="Q114" s="3" t="n">
         <v>20</v>
@@ -5617,19 +5601,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tous les cafés La Semeuse (p. ex. mocca surfin, moulu)</t>
+          <t>Tous les müeslis Farmer (p. ex. baies des bois Classic, 500 g)</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -5643,13 +5627,13 @@
         </is>
       </c>
       <c r="N115" s="2" t="n">
-        <v>13.95</v>
+        <v>4.5</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>11.16</v>
+        <v>3.6</v>
       </c>
       <c r="P115" s="2" t="n">
-        <v>2.79</v>
+        <v>0.9</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>20</v>
@@ -5666,20 +5650,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lait de coco Thai Kitchen, classique ou bio (p. ex. classique, 2 x 500 ml)</t>
+          <t>Tous les cafés La Semeuse (p. ex. mocca surfin, moulu)</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>lot de 2</t>
+          <t>à partir de 2 articles</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -5688,13 +5672,13 @@
         </is>
       </c>
       <c r="N116" s="2" t="n">
-        <v>9</v>
+        <v>13.95</v>
       </c>
       <c r="O116" s="2" t="n">
-        <v>7.2</v>
+        <v>11.16</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>1.8</v>
+        <v>2.79</v>
       </c>
       <c r="Q116" s="3" t="n">
         <v>20</v>
@@ -5711,43 +5695,38 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sucre fin cristallisé Cristal M-Classic, IP-SUISSE, 4 x 1 kg</t>
+          <t>Lait de coco Thai Kitchen, classique ou bio (p. ex. classique, 2 x 500 ml)</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>IP-Suisse</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>lot de 4</t>
+          <t>lot de 2</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="N117" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O117" s="2" t="n">
         <v>7.2</v>
-      </c>
-      <c r="O117" s="2" t="n">
-        <v>5.4</v>
       </c>
       <c r="P117" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="Q117" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118">
@@ -5761,43 +5740,43 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cafés instantanés Cafino (excepté bio), Classic et Voncoré (p. ex. Classic, 550 g)</t>
+          <t>Sucre fin cristallisé Cristal M-Classic, IP-SUISSE, 4 x 1 kg</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Rainforest Alliance</t>
+          <t>IP-Suisse</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>à partir de 2 articles</t>
+          <t>lot de 4</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="N118" s="2" t="n">
-        <v>11.8</v>
+        <v>7.2</v>
       </c>
       <c r="O118" s="2" t="n">
-        <v>8.26</v>
+        <v>5.4</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>3.54</v>
+        <v>1.8</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119">
@@ -5811,15 +5790,15 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Branches Frey, Milk ou Dark, 50 x 27 g (p. ex. Milk)</t>
+          <t>Cafés instantanés Cafino (excepté bio), Classic et Voncoré (p. ex. Classic, 550 g)</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5829,20 +5808,25 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>à partir de 2 articles</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>30%</t>
         </is>
       </c>
       <c r="N119" s="2" t="n">
-        <v>25.5</v>
+        <v>11.8</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>12.75</v>
+        <v>8.26</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>12.75</v>
+        <v>3.54</v>
       </c>
       <c r="Q119" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120">
@@ -5856,7 +5840,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Plaques de chocolat Frey assorties, 20 x 100 g</t>
+          <t>Branches Frey, Milk ou Dark, 50 x 27 g (p. ex. Milk)</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -5874,25 +5858,20 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>lot de 20</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="N120" s="2" t="n">
-        <v>48.4</v>
+        <v>25.5</v>
       </c>
       <c r="O120" s="2" t="n">
-        <v>28.95</v>
+        <v>12.75</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>19.45</v>
+        <v>12.75</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>40.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="121">
@@ -5906,7 +5885,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chocolat Ovomaltine, diverses variétés (p. ex. Ovo rocks, 2 x 120 g)</t>
+          <t>Plaques de chocolat Frey assorties, 20 x 100 g</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -5917,27 +5896,32 @@
           <t>7.1</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>lot de 2</t>
+          <t>lot de 20</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="N121" s="2" t="n">
-        <v>9.4</v>
+        <v>48.4</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>7.5</v>
+        <v>28.95</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>1.9</v>
+        <v>19.45</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>20.2</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="122">
@@ -5951,7 +5935,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boules de chocolat au lait Lindor Lindt, 3 x 200 g</t>
+          <t>Chocolat Ovomaltine, diverses variétés (p. ex. Ovo rocks, 2 x 120 g)</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -5964,25 +5948,25 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>lot de 3</t>
+          <t>lot de 2</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="N122" s="2" t="n">
-        <v>38.85</v>
+        <v>9.4</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>25.95</v>
+        <v>7.5</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>33.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="123">
@@ -5996,7 +5980,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kägi Fret en sachet, Classic, noisette ou orange, 250 g</t>
+          <t>Boules de chocolat au lait Lindor Lindt, 3 x 200 g</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -6009,15 +5993,26 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Hit</t>
-        </is>
-      </c>
-      <c r="N123" s="2" t="n"/>
+          <t>lot de 3</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>38.85</v>
+      </c>
       <c r="O123" s="2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="P123" s="2" t="n"/>
-      <c r="Q123" s="3" t="n"/>
+        <v>25.95</v>
+      </c>
+      <c r="P123" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q123" s="3" t="n">
+        <v>33.2</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6030,7 +6025,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bâtonnets de glace Choquello Praliné, Exotic Mini ou Exotic, surgelés (p. ex. Choquello Praliné, 8 x 82 ml)</t>
+          <t>Kägi Fret en sachet, Classic, noisette ou orange, 250 g</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -6041,33 +6036,17 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Rainforest Alliance</t>
-        </is>
-      </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>à partir de 2 articles</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>7.5</v>
-      </c>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="n"/>
       <c r="O124" s="2" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="P124" s="2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q124" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>5.75</v>
+      </c>
+      <c r="P124" s="2" t="n"/>
+      <c r="Q124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6076,47 +6055,47 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fraises, la barquette de 500 g (p. ex. Suisse)</t>
+          <t>Bâtonnets de glace Choquello Praliné, Exotic Mini ou Exotic, surgelés (p. ex. Choquello Praliné, 8 x 82 ml)</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Suisse ou Pays-Bas</t>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>à partir de 2 articles</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Offre de fin de semaine (18.6–21.6.2026)</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="N125" s="2" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>4.2</v>
+        <v>5.63</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>30</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="126">
@@ -6130,20 +6109,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tous les sandwiches Migros et les toasts American Favorites, IP-SUISSE</t>
+          <t>Fraises, la barquette de 500 g (p. ex. Suisse)</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>IP-Suisse</t>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Suisse ou Pays-Bas</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -6156,10 +6135,18 @@
           <t>Offre de fin de semaine (18.6–21.6.2026)</t>
         </is>
       </c>
-      <c r="N126" s="2" t="n"/>
-      <c r="O126" s="2" t="n"/>
-      <c r="P126" s="2" t="n"/>
-      <c r="Q126" s="3" t="n"/>
+      <c r="N126" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O126" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P126" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q126" s="3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6172,15 +6159,15 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Steaks de filet de porc marinés IP-SUISSE, les 100 g</t>
+          <t>Tous les sandwiches Migros et les toasts American Favorites, IP-SUISSE</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6190,7 +6177,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -6198,67 +6185,59 @@
           <t>Offre de fin de semaine (18.6–21.6.2026)</t>
         </is>
       </c>
-      <c r="N127" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O127" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P127" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q127" s="3" t="n">
-        <v>42.1</v>
-      </c>
+      <c r="N127" s="2" t="n"/>
+      <c r="O127" s="2" t="n"/>
+      <c r="P127" s="2" t="n"/>
+      <c r="Q127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Semaine 23_Lidl.pdf</t>
+          <t>Migros-Wochenflyer-25-2026-f-VD.pdf</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fraises, 500 g</t>
+          <t>Steaks de filet de porc marinés IP-SUISSE, les 100 g</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Suisse</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Qualité Suisse</t>
+          <t>IP-Suisse</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>-33%</t>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Offre de fin de semaine (18.6–21.6.2026)</t>
         </is>
       </c>
       <c r="N128" s="2" t="n">
-        <v>5.99</v>
+        <v>2.85</v>
       </c>
       <c r="O128" s="2" t="n">
-        <v>3.99</v>
+        <v>1.65</v>
       </c>
       <c r="P128" s="2" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>33.4</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="129">
@@ -6272,38 +6251,43 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fisher's Choice Filets de saumon bio</t>
+          <t>Fraises, 500 g</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Suisse</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>-41%</t>
+          <t>-33%</t>
         </is>
       </c>
       <c r="N129" s="2" t="n">
-        <v>16.99</v>
+        <v>5.99</v>
       </c>
       <c r="O129" s="2" t="n">
-        <v>9.99</v>
+        <v>3.99</v>
       </c>
       <c r="P129" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="130">
@@ -6317,43 +6301,38 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Malvoisie AOC</t>
+          <t>Fisher's Choice Filets de saumon bio</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>-33%</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
+          <t>-41%</t>
         </is>
       </c>
       <c r="N130" s="2" t="n">
-        <v>11.95</v>
+        <v>16.99</v>
       </c>
       <c r="O130" s="2" t="n">
-        <v>7.95</v>
+        <v>9.99</v>
       </c>
       <c r="P130" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q130" s="3" t="n">
-        <v>33.5</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="131">
@@ -6367,38 +6346,44 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Qualité Suisse Viande hachée mélangée allégée</t>
+          <t>Malvoisie AOC</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Qualité Suisse</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Suisse Garantie</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N131" s="2" t="n"/>
+          <t>-33%</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>11.95</v>
+      </c>
       <c r="O131" s="2" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="P131" s="2" t="n"/>
-      <c r="Q131" s="3" t="n"/>
+        <v>7.95</v>
+      </c>
+      <c r="P131" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q131" s="3" t="n">
+        <v>33.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6411,34 +6396,38 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Allini Secco</t>
+          <t>Qualité Suisse Viande hachée mélangée allégée</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Suisse Garantie</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>-25%</t>
-        </is>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>1.59</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="n"/>
       <c r="O132" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P132" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q132" s="3" t="n">
-        <v>25.2</v>
-      </c>
+        <v>12.99</v>
+      </c>
+      <c r="P132" s="2" t="n"/>
+      <c r="Q132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6447,47 +6436,38 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Qualité Suisse Plat de grillades de fête, 550 g</t>
+          <t>Allini Secco</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Suisse</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Suisse Garantie</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N133" s="2" t="n"/>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>1.59</v>
+      </c>
       <c r="O133" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="P133" s="2" t="n"/>
-      <c r="Q133" s="3" t="n"/>
+        <v>1.19</v>
+      </c>
+      <c r="P133" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q133" s="3" t="n">
+        <v>25.2</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6496,11 +6476,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nautica Saumon fumé GGN, 170 g</t>
+          <t>Duc de Coeur Filet de poitrine de canard de Barbarie, surgelé</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -6508,28 +6488,13 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Norvège</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>GGN</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N134" s="2" t="n"/>
-      <c r="O134" s="2" t="n">
-        <v>3.99</v>
-      </c>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="O134" s="2" t="n"/>
       <c r="P134" s="2" t="n"/>
       <c r="Q134" s="3" t="n"/>
     </row>
@@ -6544,20 +6509,25 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Qualité Suisse Baguette rustique Terra Natura, 410 g</t>
+          <t>Qualité Suisse Plat de grillades de fête, 550 g</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Suisse</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Terra Natura</t>
+          <t>Suisse Garantie</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6567,26 +6537,15 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>-16%</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus -33% (1.99)</t>
-        </is>
-      </c>
-      <c r="N135" s="2" t="n">
-        <v>2.99</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="n"/>
       <c r="O135" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P135" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q135" s="3" t="n">
-        <v>16.7</v>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="P135" s="2" t="n"/>
+      <c r="Q135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6599,7 +6558,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ocean Sea Bâtonnets de poisson MSC, surgelés, 15 pièces, 450 g</t>
+          <t>Nautica Saumon fumé GGN, 170 g</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -6610,28 +6569,27 @@
           <t>5.3</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Norvège</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>GGN</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>-40%</t>
-        </is>
-      </c>
-      <c r="N136" s="2" t="n">
-        <v>2.99</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="n"/>
       <c r="O136" s="2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P136" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q136" s="3" t="n">
-        <v>40.1</v>
-      </c>
+        <v>3.99</v>
+      </c>
+      <c r="P136" s="2" t="n"/>
+      <c r="Q136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6644,25 +6602,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Qualité Suisse Escalopes de filet de porc ultra fines, pack de 2 XXL, 2 x 380 g</t>
+          <t>Qualité Suisse Baguette rustique Terra Natura, 410 g</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Suisse</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Suisse Garantie</t>
+          <t>Terra Natura</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6672,15 +6625,26 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N137" s="2" t="n"/>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus -33% (1.99)</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>2.99</v>
+      </c>
       <c r="O137" s="2" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="P137" s="2" t="n"/>
-      <c r="Q137" s="3" t="n"/>
+        <v>2.49</v>
+      </c>
+      <c r="P137" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q137" s="3" t="n">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6689,52 +6653,42 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mont-sur-Rolle La Côte AOC, 75 cl</t>
+          <t>Ocean Sea Bâtonnets de poisson MSC, surgelés, 15 pièces, 450 g</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Suisse – Vaud</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
+          <t>-40%</t>
         </is>
       </c>
       <c r="N138" s="2" t="n">
-        <v>6.79</v>
+        <v>2.99</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>5.39</v>
+        <v>1.79</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>20.6</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="139">
@@ -6744,19 +6698,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cœurs de laitues pommées suisses, 2 pièces</t>
+          <t>Qualité Suisse Escalopes de filet de porc ultra fines, pack de 2 XXL, 2 x 380 g</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -6769,23 +6723,22 @@
           <t>Suisse Garantie</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>-28%</t>
-        </is>
-      </c>
-      <c r="N139" s="2" t="n">
-        <v>3.49</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="n"/>
       <c r="O139" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P139" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q139" s="3" t="n">
-        <v>28.7</v>
-      </c>
+        <v>12.99</v>
+      </c>
+      <c r="P139" s="2" t="n"/>
+      <c r="Q139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6798,33 +6751,48 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dulano Selection Bâtonnets de salami, classiques ou piquants, 100 g</t>
+          <t>Mont-sur-Rolle La Côte AOC, 75 cl</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Suisse – Vaud</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>AOC</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
         </is>
       </c>
       <c r="N140" s="2" t="n">
-        <v>3.79</v>
+        <v>6.79</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>2.99</v>
+        <v>5.39</v>
       </c>
       <c r="P140" s="2" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="141">
@@ -6838,38 +6806,43 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Freeway Mate, diverses sortes, 33 cl</t>
+          <t>Cœurs de laitues pommées suisses, 2 pièces</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Suisse</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Suisse Garantie</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus -30% (0.69)</t>
+          <t>-28%</t>
         </is>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.99</v>
+        <v>3.49</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>0.79</v>
+        <v>2.49</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>20.2</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="142">
@@ -6883,28 +6856,34 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sprite, pack de 24, 24 x 33 cl</t>
+          <t>Dulano Selection Bâtonnets de salami, classiques ou piquants, 100 g</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N142" s="2" t="n"/>
+          <t>-21%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>3.79</v>
+      </c>
       <c r="O142" s="2" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="P142" s="2" t="n"/>
-      <c r="Q142" s="3" t="n"/>
+        <v>2.99</v>
+      </c>
+      <c r="P142" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q142" s="3" t="n">
+        <v>21.1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6913,37 +6892,42 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chef Select Bowl de salade, diverses sortes, 300 g</t>
+          <t>Freeway Mate, diverses sortes, 33 cl</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus -30% (0.69)</t>
         </is>
       </c>
       <c r="N143" s="2" t="n">
-        <v>4.95</v>
+        <v>0.99</v>
       </c>
       <c r="O143" s="2" t="n">
-        <v>3.69</v>
+        <v>0.79</v>
       </c>
       <c r="P143" s="2" t="n">
-        <v>1.26</v>
+        <v>0.2</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>25.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="144">
@@ -6953,48 +6937,32 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Abricots, le kg</t>
+          <t>Sprite, pack de 24, 24 x 33 cl</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Espagne, Italie</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>-31%</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus -34% (3.79)</t>
-        </is>
-      </c>
-      <c r="N144" s="2" t="n">
-        <v>5.79</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="n"/>
       <c r="O144" s="2" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="P144" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q144" s="3" t="n">
-        <v>31.1</v>
-      </c>
+        <v>12.95</v>
+      </c>
+      <c r="P144" s="2" t="n"/>
+      <c r="Q144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7003,11 +6971,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fraises, 500 g</t>
+          <t>Chef Select Bowl de salade, diverses sortes, 300 g</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -7015,35 +6983,25 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Suisse</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>-33%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="N145" s="2" t="n">
-        <v>5.99</v>
+        <v>4.95</v>
       </c>
       <c r="O145" s="2" t="n">
-        <v>3.99</v>
+        <v>3.69</v>
       </c>
       <c r="P145" s="2" t="n">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="Q145" s="3" t="n">
-        <v>33.4</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="146">
@@ -7053,11 +7011,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pastèque, le kg</t>
+          <t>Abricots, le kg</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -7075,20 +7033,25 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>-33%</t>
+          <t>-31%</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus -34% (3.79)</t>
         </is>
       </c>
       <c r="N146" s="2" t="n">
-        <v>1.79</v>
+        <v>5.79</v>
       </c>
       <c r="O146" s="2" t="n">
-        <v>1.19</v>
+        <v>3.99</v>
       </c>
       <c r="P146" s="2" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q146" s="3" t="n">
-        <v>33.5</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="147">
@@ -7098,32 +7061,48 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Feuilleté carbonara, 119 g</t>
+          <t>Fraises, 500 g</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Suisse</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N147" s="2" t="n"/>
+          <t>-33%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>5.99</v>
+      </c>
       <c r="O147" s="2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P147" s="2" t="n"/>
-      <c r="Q147" s="3" t="n"/>
+        <v>3.99</v>
+      </c>
+      <c r="P147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q147" s="3" t="n">
+        <v>33.4</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7132,37 +7111,42 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Croissant jambon-fromage, 3 x 95 g</t>
+          <t>Pastèque, le kg</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Espagne, Italie</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2+1 gratuit</t>
+          <t>-33%</t>
         </is>
       </c>
       <c r="N148" s="2" t="n">
-        <v>4.47</v>
+        <v>1.79</v>
       </c>
       <c r="O148" s="2" t="n">
-        <v>2.98</v>
+        <v>1.19</v>
       </c>
       <c r="P148" s="2" t="n">
-        <v>1.49</v>
+        <v>0.6</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="149">
@@ -7176,7 +7160,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Chausson à la cannelle, 113 g</t>
+          <t>Feuilleté carbonara, 119 g</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -7184,7 +7168,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -7194,7 +7178,7 @@
       </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="2" t="n">
-        <v>0.99</v>
+        <v>1.49</v>
       </c>
       <c r="P149" s="2" t="n"/>
       <c r="Q149" s="3" t="n"/>
@@ -7210,7 +7194,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Croissant fourré au praliné noisette, 85 g</t>
+          <t>Croissant jambon-fromage, 3 x 95 g</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -7218,25 +7202,25 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>-28%</t>
+          <t>2+1 gratuit</t>
         </is>
       </c>
       <c r="N150" s="2" t="n">
-        <v>1.39</v>
+        <v>4.47</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>0.99</v>
+        <v>2.98</v>
       </c>
       <c r="P150" s="2" t="n">
-        <v>0.4</v>
+        <v>1.49</v>
       </c>
       <c r="Q150" s="3" t="n">
-        <v>28.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="151">
@@ -7250,44 +7234,28 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Qualité Suisse Couronne de Sils, 360 g</t>
+          <t>Chausson à la cannelle, 113 g</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>-30%</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
-      <c r="N151" s="2" t="n">
-        <v>2.79</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="n"/>
       <c r="O151" s="2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P151" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="Q151" s="3" t="n">
-        <v>30.1</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="P151" s="2" t="n"/>
+      <c r="Q151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7300,38 +7268,34 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Fisher's Choice Filets de silure requin croustillants ASC XXL, 500 g</t>
+          <t>Croissant fourré au praliné noisette, 85 g</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>ASC</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N152" s="2" t="n"/>
+          <t>-28%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>1.39</v>
+      </c>
       <c r="O152" s="2" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="P152" s="2" t="n"/>
-      <c r="Q152" s="3" t="n"/>
+        <v>0.99</v>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q152" s="3" t="n">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7344,43 +7308,43 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Fisher's Choice Filets de saumon bio, avec peau, 3 x 125 g</t>
+          <t>Qualité Suisse Couronne de Sils, 360 g</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Norvège</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>-41%</t>
+          <t>-30%</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
         </is>
       </c>
       <c r="N153" s="2" t="n">
-        <v>16.99</v>
+        <v>2.79</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>9.99</v>
+        <v>1.95</v>
       </c>
       <c r="P153" s="2" t="n">
-        <v>7</v>
+        <v>0.84</v>
       </c>
       <c r="Q153" s="3" t="n">
-        <v>41.2</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="154">
@@ -7390,11 +7354,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Qualité Suisse Viande hachée mélangée allégée, pack de 2, 2 x 370 g</t>
+          <t>Fisher's Choice Filets de silure requin croustillants ASC XXL, 500 g</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -7402,22 +7366,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Suisse</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Suisse Garantie</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -7427,7 +7386,7 @@
       </c>
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="2" t="n">
-        <v>12.99</v>
+        <v>6.95</v>
       </c>
       <c r="P154" s="2" t="n"/>
       <c r="Q154" s="3" t="n"/>
@@ -7439,11 +7398,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Deluxe Filet d'agneau mariné, 100 g</t>
+          <t>Fisher's Choice Filets de saumon bio, avec peau, 3 x 125 g</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -7451,25 +7410,36 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Irlande</t>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Bio</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N155" s="2" t="n"/>
+          <t>-41%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>16.99</v>
+      </c>
       <c r="O155" s="2" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="P155" s="2" t="n"/>
-      <c r="Q155" s="3" t="n"/>
+        <v>9.99</v>
+      </c>
+      <c r="P155" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q155" s="3" t="n">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7482,7 +7452,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Qualité Suisse Steak de cou de porc, assaisonné, 800 g</t>
+          <t>Qualité Suisse Viande hachée mélangée allégée, pack de 2, 2 x 370 g</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -7515,7 +7485,7 @@
       </c>
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="2" t="n">
-        <v>9.99</v>
+        <v>12.99</v>
       </c>
       <c r="P156" s="2" t="n"/>
       <c r="Q156" s="3" t="n"/>
@@ -7531,7 +7501,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Qualité Suisse Brochettes flambeau farcies, 400 g</t>
+          <t>Deluxe Filet d'agneau mariné, 100 g</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -7544,41 +7514,20 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Suisse</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Suisse Garantie</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
+          <t>Irlande</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>-22%</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
-      <c r="N157" s="2" t="n">
-        <v>8.99</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="n"/>
       <c r="O157" s="2" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="P157" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q157" s="3" t="n">
-        <v>22.2</v>
-      </c>
+        <v>3.29</v>
+      </c>
+      <c r="P157" s="2" t="n"/>
+      <c r="Q157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7587,43 +7536,47 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Gamellón Crianza, 75 cl</t>
+          <t>Qualité Suisse Steak de cou de porc, assaisonné, 800 g</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Espagne – Murcia</t>
+          <t>Suisse</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Suisse Garantie</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="N158" s="2" t="n">
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="n"/>
+      <c r="O158" s="2" t="n">
         <v>9.99</v>
       </c>
-      <c r="O158" s="2" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="P158" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q158" s="3" t="n">
-        <v>20</v>
-      </c>
+      <c r="P158" s="2" t="n"/>
+      <c r="Q158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7632,11 +7585,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Qualité Suisse Poitrine de dinde en tranches, barbecue ou paprika, 120 g</t>
+          <t>Qualité Suisse Brochettes flambeau farcies, 400 g</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -7644,7 +7597,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Suisse</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7659,7 +7617,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -7668,16 +7626,16 @@
         </is>
       </c>
       <c r="N159" s="2" t="n">
-        <v>4.49</v>
+        <v>8.99</v>
       </c>
       <c r="O159" s="2" t="n">
-        <v>3.59</v>
+        <v>6.99</v>
       </c>
       <c r="P159" s="2" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="Q159" s="3" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="160">
@@ -7687,11 +7645,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ocean Sea Pointes de saumon, sans peau, surgelées, 455 g</t>
+          <t>Deluxe Steak de bœuf Striploin Irish Angus, 250 g</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -7699,36 +7657,20 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>ASC</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Irlande</t>
         </is>
       </c>
       <c r="N160" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="O160" s="2" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="P160" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q160" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>14.99</v>
+      </c>
+      <c r="O160" s="2" t="n"/>
+      <c r="P160" s="2" t="n"/>
+      <c r="Q160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7737,11 +7679,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Qualité Suisse Saucisson vaudois, 100 g</t>
+          <t>Deluxe Steak de contre-filet Irish Angus, 250 g</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -7749,28 +7691,18 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Suisse Garantie</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N161" s="2" t="n"/>
-      <c r="O161" s="2" t="n">
-        <v>1.99</v>
-      </c>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Irlande</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="O161" s="2" t="n"/>
       <c r="P161" s="2" t="n"/>
       <c r="Q161" s="3" t="n"/>
     </row>
@@ -7781,11 +7713,11 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Qualité Suisse Chorizo, doux ou piquant, 150 g</t>
+          <t>Deluxe Steak de filet Irish Angus, 200 g</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -7793,36 +7725,20 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Suisse Garantie</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>-26%</t>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Irlande</t>
         </is>
       </c>
       <c r="N162" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O162" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="P162" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q162" s="3" t="n">
-        <v>26</v>
-      </c>
+        <v>18.99</v>
+      </c>
+      <c r="O162" s="2" t="n"/>
+      <c r="P162" s="2" t="n"/>
+      <c r="Q162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7831,11 +7747,11 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Qualité Suisse Viande des Grisons, classique, tranches ultra fines, 80 g / 90 g</t>
+          <t>Deluxe Steak de bœuf ribeye Irish Angus, 250 g</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -7843,36 +7759,20 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Suisse Garantie</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-20%</t>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Irlande</t>
         </is>
       </c>
       <c r="N163" s="2" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="O163" s="2" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="P163" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q163" s="3" t="n">
-        <v>20.9</v>
-      </c>
+        <v>18.99</v>
+      </c>
+      <c r="O163" s="2" t="n"/>
+      <c r="P163" s="2" t="n"/>
+      <c r="Q163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7881,19 +7781,24 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Dulano Selection Fuet Extra, 170 g</t>
+          <t>Gamellón Crianza, 75 cl</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Espagne – Murcia</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -7902,13 +7807,13 @@
         </is>
       </c>
       <c r="N164" s="2" t="n">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
       <c r="P164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q164" s="3" t="n">
         <v>20</v>
@@ -7921,30 +7826,35 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tartare L'Apéritif, Provence ou Italie, 100 g</t>
+          <t>Monte Plogar Cariñena Gran Reserva DO, 75 cl</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N165" s="2" t="n"/>
-      <c r="O165" s="2" t="n">
-        <v>2.49</v>
-      </c>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Espagne – Aragon</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="O165" s="2" t="n"/>
       <c r="P165" s="2" t="n"/>
       <c r="Q165" s="3" t="n"/>
     </row>
@@ -7955,43 +7865,32 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Vita D'or Margarine végétale, 500 g</t>
+          <t>Corte alle Mura Chianti Riserva, 75 cl</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Vegan</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>-22%</t>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Italie – Toscane</t>
         </is>
       </c>
       <c r="N166" s="2" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="O166" s="2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="P166" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q166" s="3" t="n">
-        <v>22.8</v>
-      </c>
+        <v>7.99</v>
+      </c>
+      <c r="O166" s="2" t="n"/>
+      <c r="P166" s="2" t="n"/>
+      <c r="Q166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8000,24 +7899,34 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Vita D'or Huile de colza, 1 l</t>
+          <t>Qualité Suisse Poitrine de dinde en tranches, barbecue ou paprika, 120 g</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Suisse Garantie</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -8026,16 +7935,16 @@
         </is>
       </c>
       <c r="N167" s="2" t="n">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>2.99</v>
+        <v>3.59</v>
       </c>
       <c r="P167" s="2" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168">
@@ -8045,34 +7954,29 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Qualité Suisse Lait drink riche en protéines, sans lactose, UHT, 1 l</t>
+          <t>Ocean Sea Pointes de saumon, sans peau, surgelées, 455 g</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Suisse Garantie</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -8081,16 +7985,16 @@
         </is>
       </c>
       <c r="N168" s="2" t="n">
-        <v>2.19</v>
+        <v>9.99</v>
       </c>
       <c r="O168" s="2" t="n">
-        <v>1.79</v>
+        <v>7.99</v>
       </c>
       <c r="P168" s="2" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>18.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169">
@@ -8100,43 +8004,42 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Milbona Boisson riche en protéines, vanille ou chocolat, 350 g</t>
+          <t>Qualité Suisse Saucisson vaudois, 100 g</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Suisse Garantie</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>-26%</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="n">
-        <v>1.35</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="n"/>
       <c r="O169" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="P169" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Q169" s="3" t="n">
-        <v>26.7</v>
-      </c>
+        <v>1.99</v>
+      </c>
+      <c r="P169" s="2" t="n"/>
+      <c r="Q169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8145,11 +8048,11 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Nixe Thon MSC de bonite à ventre rayé à l'huile de tournesol, 156 g</t>
+          <t>Qualité Suisse Chorizo, doux ou piquant, 150 g</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -8157,30 +8060,35 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>Suisse Garantie</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="N170" s="2" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="O170" s="2" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="P170" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q170" s="3" t="n">
-        <v>21.3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="171">
@@ -8190,42 +8098,47 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Alesto Selection Noix de cajou naturelles, 200 g</t>
+          <t>Qualité Suisse Viande des Grisons, classique, tranches ultra fines, 80 g / 90 g</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Suisse Garantie</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>-33%</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="N171" s="2" t="n">
-        <v>2.69</v>
+        <v>6.89</v>
       </c>
       <c r="O171" s="2" t="n">
-        <v>1.79</v>
+        <v>5.45</v>
       </c>
       <c r="P171" s="2" t="n">
-        <v>0.9</v>
+        <v>1.44</v>
       </c>
       <c r="Q171" s="3" t="n">
-        <v>33.5</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="172">
@@ -8235,19 +8148,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Alesto Selection Mélange de fruits à coque, 200 g</t>
+          <t>Dulano Selection Fuet Extra, 170 g</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -8255,22 +8168,17 @@
           <t>-20%</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
       <c r="N172" s="2" t="n">
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
       <c r="O172" s="2" t="n">
-        <v>2.39</v>
+        <v>3.99</v>
       </c>
       <c r="P172" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q172" s="3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
@@ -8280,38 +8188,32 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chef Select Beignets aux pommes, surgelés, 300 g</t>
+          <t>Tartare L'Apéritif, Provence ou Italie, 100 g</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>-16%</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="n">
-        <v>3.59</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="n"/>
       <c r="O173" s="2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P173" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q173" s="3" t="n">
-        <v>16.7</v>
-      </c>
+        <v>2.49</v>
+      </c>
+      <c r="P173" s="2" t="n"/>
+      <c r="Q173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8320,32 +8222,43 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Langnese Magnum White, surgelés, 8 x 100 ml</t>
+          <t>Vita D'or Margarine végétale, 500 g</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Vegan</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N174" s="2" t="n"/>
+          <t>-22%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>2.19</v>
+      </c>
       <c r="O174" s="2" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="P174" s="2" t="n"/>
-      <c r="Q174" s="3" t="n"/>
+        <v>1.69</v>
+      </c>
+      <c r="P174" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q174" s="3" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8358,28 +8271,39 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Mövenpick Branche Cailler ou Coco Paradise, surgelés, 900 ml</t>
+          <t>Vita D'or Huile de colza, 1 l</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="n"/>
+          <t>-14%</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>3.49</v>
+      </c>
       <c r="O175" s="2" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="P175" s="2" t="n"/>
-      <c r="Q175" s="3" t="n"/>
+        <v>2.99</v>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q175" s="3" t="n">
+        <v>14.3</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8392,33 +8316,48 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bilz Panaché sans alcool, 10 x 33 cl</t>
+          <t>Qualité Suisse Lait drink riche en protéines, sans lactose, UHT, 1 l</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Suisse Garantie</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-18%</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
         </is>
       </c>
       <c r="N176" s="2" t="n">
-        <v>14.49</v>
+        <v>2.19</v>
       </c>
       <c r="O176" s="2" t="n">
-        <v>10.85</v>
+        <v>1.79</v>
       </c>
       <c r="P176" s="2" t="n">
-        <v>3.64</v>
+        <v>0.4</v>
       </c>
       <c r="Q176" s="3" t="n">
-        <v>25.1</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="177">
@@ -8432,7 +8371,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Perlenbacher Radler nature sans alcool, 50 cl</t>
+          <t>Milbona Boisson riche en protéines, vanille ou chocolat, 350 g</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -8445,20 +8384,25 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-26%</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
         </is>
       </c>
       <c r="N177" s="2" t="n">
-        <v>0.49</v>
+        <v>1.35</v>
       </c>
       <c r="O177" s="2" t="n">
-        <v>0.39</v>
+        <v>0.99</v>
       </c>
       <c r="P177" s="2" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="Q177" s="3" t="n">
-        <v>20.4</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="178">
@@ -8468,32 +8412,43 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Solevita Boissons Funny Fruit, Cola Lemon ou Tropical, 14 x 20 cl</t>
+          <t>Nixe Thon MSC de bonite à ventre rayé à l'huile de tournesol, 156 g</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>MSC</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="n"/>
+          <t>-21%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>2.35</v>
+      </c>
       <c r="O178" s="2" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="P178" s="2" t="n"/>
-      <c r="Q178" s="3" t="n"/>
+        <v>1.85</v>
+      </c>
+      <c r="P178" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q178" s="3" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8502,42 +8457,42 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Cave Aliança Casal Mendes Rosé, 75 cl</t>
+          <t>Alesto Selection Noix de cajou naturelles, 200 g</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Portugal</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>-38%</t>
+          <t>-33%</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
         </is>
       </c>
       <c r="N179" s="2" t="n">
-        <v>5.95</v>
+        <v>2.69</v>
       </c>
       <c r="O179" s="2" t="n">
-        <v>3.65</v>
+        <v>1.79</v>
       </c>
       <c r="P179" s="2" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q179" s="3" t="n">
-        <v>38.7</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="180">
@@ -8547,47 +8502,42 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Torre de Ferro Dão Reserva DOC, 75 cl</t>
+          <t>Alesto Selection Mélange de fruits à coque, 200 g</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Portugal – Dão</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>DOC</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
         </is>
       </c>
       <c r="N180" s="2" t="n">
-        <v>3.59</v>
+        <v>2.99</v>
       </c>
       <c r="O180" s="2" t="n">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="P180" s="2" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="Q180" s="3" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="181">
@@ -8597,11 +8547,11 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Somersby Apple Original, 4,5% vol., 4 x 50 cl</t>
+          <t>Chef Select Beignets aux pommes, surgelés, 300 g</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -8609,25 +8559,25 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="N181" s="2" t="n">
-        <v>11.49</v>
+        <v>3.59</v>
       </c>
       <c r="O181" s="2" t="n">
-        <v>8.59</v>
+        <v>2.99</v>
       </c>
       <c r="P181" s="2" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="Q181" s="3" t="n">
-        <v>25.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="182">
@@ -8637,11 +8587,11 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Gamellón Crianza, 75 cl</t>
+          <t>Langnese Magnum White, surgelés, 8 x 100 ml</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -8649,31 +8599,20 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Espagne – Murcia</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="n">
-        <v>9.99</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="n"/>
       <c r="O182" s="2" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="P182" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q182" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>8.949999999999999</v>
+      </c>
+      <c r="P182" s="2" t="n"/>
+      <c r="Q182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8682,11 +8621,11 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Malvoisie AOC, 75 cl</t>
+          <t>Mövenpick Branche Cailler ou Coco Paradise, surgelés, 900 ml</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -8694,41 +8633,20 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Suisse – Valais</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>AOC</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>-33%</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="n">
-        <v>11.95</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="n"/>
       <c r="O183" s="2" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="P183" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q183" s="3" t="n">
-        <v>33.5</v>
-      </c>
+        <v>9.050000000000001</v>
+      </c>
+      <c r="P183" s="2" t="n"/>
+      <c r="Q183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8737,11 +8655,11 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Deluxe Pralinés façon Dubaï, 120 g (article non disponible)</t>
+          <t>Bilz Panaché sans alcool, 10 x 33 cl</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -8749,35 +8667,25 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>Rabais d'introduction</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="N184" s="2" t="n">
-        <v>4.99</v>
+        <v>14.49</v>
       </c>
       <c r="O184" s="2" t="n">
-        <v>3.99</v>
+        <v>10.85</v>
       </c>
       <c r="P184" s="2" t="n">
-        <v>1</v>
+        <v>3.64</v>
       </c>
       <c r="Q184" s="3" t="n">
-        <v>20</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="185">
@@ -8787,29 +8695,19 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Qualité Suisse Séré maigre sans lactose, 250 g</t>
+          <t>Perlenbacher Radler nature sans alcool, 50 cl</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Qualité Suisse</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Suisse Garantie</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -8817,27 +8715,17 @@
           <t>-20%</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>Rabais d'introduction</t>
-        </is>
-      </c>
       <c r="N185" s="2" t="n">
-        <v>1.19</v>
+        <v>0.49</v>
       </c>
       <c r="O185" s="2" t="n">
-        <v>0.95</v>
+        <v>0.39</v>
       </c>
       <c r="P185" s="2" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="Q185" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="186">
@@ -8847,11 +8735,11 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cheetos XL fromage et paprika, 130 g (retard dans la livraison)</t>
+          <t>Gordon's Gin sans alcool, 70 cl</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -8859,36 +8747,15 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>Rabais d'introduction</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="N186" s="2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="O186" s="2" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="P186" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="Q186" s="3" t="n">
-        <v>20.1</v>
-      </c>
+        <v>18.45</v>
+      </c>
+      <c r="O186" s="2" t="n"/>
+      <c r="P186" s="2" t="n"/>
+      <c r="Q186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8901,44 +8768,28 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Crownfield Granola Honey, au miel, 500 g</t>
+          <t>Solevita Boissons Funny Fruit, Cola Lemon ou Tropical, 14 x 20 cl</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>Avec Lidl Plus</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>Rabais d'introduction</t>
-        </is>
-      </c>
-      <c r="N187" s="2" t="n">
-        <v>3.29</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="n"/>
       <c r="O187" s="2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P187" s="2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="Q187" s="3" t="n">
-        <v>20.1</v>
-      </c>
+        <v>3.49</v>
+      </c>
+      <c r="P187" s="2" t="n"/>
+      <c r="Q187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8947,11 +8798,11 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Fanta, pack de 24, Orange ou Exotic, 24 x 33 cl</t>
+          <t>Cave Aliança Casal Mendes Rosé, 75 cl</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -8959,20 +8810,31 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N188" s="2" t="n"/>
+          <t>-38%</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>5.95</v>
+      </c>
       <c r="O188" s="2" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="P188" s="2" t="n"/>
-      <c r="Q188" s="3" t="n"/>
+        <v>3.65</v>
+      </c>
+      <c r="P188" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q188" s="3" t="n">
+        <v>38.7</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8981,11 +8843,11 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Coca-Cola, pack de 24, classique ou zéro, 24 x 33 cl</t>
+          <t>Torre de Ferro Dão Reserva DOC, 75 cl</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -8993,20 +8855,36 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Portugal – Dão</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>DOC</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="n"/>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="n">
+        <v>3.59</v>
+      </c>
       <c r="O189" s="2" t="n">
-        <v>13.19</v>
-      </c>
-      <c r="P189" s="2" t="n"/>
-      <c r="Q189" s="3" t="n"/>
+        <v>3.05</v>
+      </c>
+      <c r="P189" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q189" s="3" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9015,37 +8893,37 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Nescafé Dolce Gusto Capsules de café, diverses sortes, 30 pièces</t>
+          <t>Somersby Apple Original, 4,5% vol., 4 x 50 cl</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>-33%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="N190" s="2" t="n">
-        <v>11.89</v>
+        <v>11.49</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>7.95</v>
+        <v>8.59</v>
       </c>
       <c r="P190" s="2" t="n">
-        <v>3.94</v>
+        <v>2.9</v>
       </c>
       <c r="Q190" s="3" t="n">
-        <v>33.1</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="191">
@@ -9055,37 +8933,42 @@
         </is>
       </c>
       <c r="B191" t="n">
+        <v>17</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Gamellón Crianza, 75 cl</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>7</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Espagne – Murcia</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O191" s="2" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="P191" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q191" s="3" t="n">
         <v>20</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Maggi Arôme liquide, 250 g</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>7</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="O191" s="2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P191" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q191" s="3" t="n">
-        <v>20.8</v>
       </c>
     </row>
     <row r="192">
@@ -9095,37 +8978,52 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Nestlé Bouillie au lait, banane-fraises ou banane-pommes, 450 g</t>
+          <t>Malvoisie AOC, 75 cl</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Suisse – Valais</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>AOC</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>-24%</t>
+          <t>-33%</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
         </is>
       </c>
       <c r="N192" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>11.95</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>6.75</v>
+        <v>7.95</v>
       </c>
       <c r="P192" s="2" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="Q192" s="3" t="n">
-        <v>24.1</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="193">
@@ -9135,37 +9033,47 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nestlé Bouillie aux céréales, 8 céréales ou multi-céréales Pyjama, 160 g</t>
+          <t>Deluxe Pralinés façon Dubaï, 120 g (article non disponible)</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Rabais d'introduction</t>
         </is>
       </c>
       <c r="N193" s="2" t="n">
-        <v>3.49</v>
+        <v>4.99</v>
       </c>
       <c r="O193" s="2" t="n">
-        <v>3.15</v>
+        <v>3.99</v>
       </c>
       <c r="P193" s="2" t="n">
-        <v>0.34</v>
+        <v>1</v>
       </c>
       <c r="Q193" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194">
@@ -9175,37 +9083,57 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Allini Secco, Rosato ou Bianco, 20 cl</t>
+          <t>Qualité Suisse Séré maigre sans lactose, 250 g</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Qualité Suisse</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Suisse Garantie</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Rabais d'introduction</t>
         </is>
       </c>
       <c r="N194" s="2" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>1.19</v>
+        <v>0.95</v>
       </c>
       <c r="P194" s="2" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="Q194" s="3" t="n">
-        <v>25.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="195">
@@ -9215,11 +9143,11 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Allini Prosecco DOC, 37,5 cl</t>
+          <t>Cheetos XL fromage et paprika, 130 g (retard dans la livraison)</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -9227,17 +9155,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Italie – Vénétie</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>DOC</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -9245,17 +9163,27 @@
           <t>-20%</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Rabais d'introduction</t>
+        </is>
+      </c>
       <c r="N195" s="2" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="P195" s="2" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="Q195" s="3" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="196">
@@ -9265,11 +9193,11 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italiamo Sfogliatine Glassate, 200 g</t>
+          <t>Crownfield Granola Honey, au miel, 500 g</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -9282,7 +9210,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -9290,17 +9218,22 @@
           <t>Avec Lidl Plus</t>
         </is>
       </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Rabais d'introduction</t>
+        </is>
+      </c>
       <c r="N196" s="2" t="n">
-        <v>1.99</v>
+        <v>3.29</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>1.49</v>
+        <v>2.63</v>
       </c>
       <c r="P196" s="2" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="Q196" s="3" t="n">
-        <v>25.1</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="197">
@@ -9310,11 +9243,11 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Fantini Farnese Edizione Cinque Autoctoni, 75 cl</t>
+          <t>Fanta, pack de 24, Orange ou Exotic, 24 x 33 cl</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -9322,31 +9255,20 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Italie</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>-40%</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="n">
-        <v>27.95</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="n"/>
       <c r="O197" s="2" t="n">
-        <v>16.65</v>
-      </c>
-      <c r="P197" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="Q197" s="3" t="n">
-        <v>40.4</v>
-      </c>
+        <v>12.95</v>
+      </c>
+      <c r="P197" s="2" t="n"/>
+      <c r="Q197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9355,11 +9277,11 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Allini Moscato Spumante Dolce, 75 cl</t>
+          <t>Coca-Cola, pack de 24, classique ou zéro, 24 x 33 cl</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -9367,31 +9289,20 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Italie</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>-25%</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="n">
-        <v>3.95</v>
-      </c>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="n"/>
       <c r="O198" s="2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P198" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q198" s="3" t="n">
-        <v>25.3</v>
-      </c>
+        <v>13.19</v>
+      </c>
+      <c r="P198" s="2" t="n"/>
+      <c r="Q198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9400,42 +9311,37 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Più Secco, 75 cl</t>
+          <t>Nescafé Dolce Gusto Capsules de café, diverses sortes, 30 pièces</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Italie</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-33%</t>
         </is>
       </c>
       <c r="N199" s="2" t="n">
-        <v>2.75</v>
+        <v>11.89</v>
       </c>
       <c r="O199" s="2" t="n">
-        <v>2.19</v>
+        <v>7.95</v>
       </c>
       <c r="P199" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="Q199" s="3" t="n">
-        <v>20.4</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="200">
@@ -9445,11 +9351,11 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Maestro de Pigo Primitivo di Manduria DOC, 75 cl</t>
+          <t>Maggi Arôme liquide, 250 g</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -9457,35 +9363,25 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Italie – Pouilles</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>DOC</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>-28%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="N200" s="2" t="n">
-        <v>6.99</v>
+        <v>2.89</v>
       </c>
       <c r="O200" s="2" t="n">
-        <v>4.99</v>
+        <v>2.29</v>
       </c>
       <c r="P200" s="2" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="Q200" s="3" t="n">
-        <v>28.6</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="201">
@@ -9495,38 +9391,27 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Evian Eau minérale plate, 6 x 1,5 l</t>
+          <t>Thomy Mayonnaise / Thomynaise light, 2 x 265 g / 2 x 280 g</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-50% en pack de 6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="N201" s="2" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="O201" s="2" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="P201" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q201" s="3" t="n">
-        <v>50.1</v>
-      </c>
+        <v>4.69</v>
+      </c>
+      <c r="O201" s="2" t="n"/>
+      <c r="P201" s="2" t="n"/>
+      <c r="Q201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9535,51 +9420,1924 @@
         </is>
       </c>
       <c r="B202" t="n">
+        <v>20</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Thomy Sauce à salades, diverses sortes, 2 x 700 ml</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>6</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="O202" s="2" t="n"/>
+      <c r="P202" s="2" t="n"/>
+      <c r="Q202" s="3" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>20</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Nestlé Yogolino, biscuit ou vanille, 4 x 100 g</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>8</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="N203" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O203" s="2" t="n"/>
+      <c r="P203" s="2" t="n"/>
+      <c r="Q203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>22</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Nestlé Bouillie au lait, banane-fraises ou banane-pommes, 450 g</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>8</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="O204" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P204" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q204" s="3" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>22</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Nestlé Bouillie aux céréales, 8 céréales ou multi-céréales Pyjama, 160 g</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>8</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="O205" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P205" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Q205" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>22</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Cailler Tablettes de chocolat, pack de 3, diverses sortes, 600 g</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>7</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="O206" s="2" t="n"/>
+      <c r="P206" s="2" t="n"/>
+      <c r="Q206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>22</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Cailler Tablette de chocolat XXL, diverses sortes, 2 kg</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>7</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="O207" s="2" t="n"/>
+      <c r="P207" s="2" t="n"/>
+      <c r="Q207" s="3" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>22</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Cailler Mini branches au lait, 1 kg</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>7</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="O208" s="2" t="n"/>
+      <c r="P208" s="2" t="n"/>
+      <c r="Q208" s="3" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>22</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Cailler Branches, diverses sortes, 690 g</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>7</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="O209" s="2" t="n"/>
+      <c r="P209" s="2" t="n"/>
+      <c r="Q209" s="3" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>23</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Bon Gelati Mini Mix amandes, chocolat au lait ou chocolat blanc, surgelés, 12 x 50 ml</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>7</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="O210" s="2" t="n"/>
+      <c r="P210" s="2" t="n"/>
+      <c r="Q210" s="3" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>23</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Bon Gelati Bâtonnets glacés fraise croustillante, surgelés, 6 x 100 ml</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>7</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O211" s="2" t="n"/>
+      <c r="P211" s="2" t="n"/>
+      <c r="Q211" s="3" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>23</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Gelatelli Mini glace au café, surgelés, 8 x 38 ml</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>7</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Fairtrade Max Havelaar</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="O212" s="2" t="n"/>
+      <c r="P212" s="2" t="n"/>
+      <c r="Q212" s="3" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>25</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Gelatelli Bâtonnets glacés double, diverses sortes, surgelés, 4 x 85 ml / 4 x 90 ml</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>7</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O213" s="2" t="n"/>
+      <c r="P213" s="2" t="n"/>
+      <c r="Q213" s="3" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>25</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Bon Gelati Bâtonnets glacés aux amandes, surgelés, 6 x 100 ml</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>7</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O214" s="2" t="n"/>
+      <c r="P214" s="2" t="n"/>
+      <c r="Q214" s="3" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>25</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Bon Gelati Mini Mix, surgelés, 12 x 50 ml</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>7</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O215" s="2" t="n"/>
+      <c r="P215" s="2" t="n"/>
+      <c r="Q215" s="3" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>25</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Bon Gelati Bâtonnets glacés crisp, vanille, blanc, surgelés, 6 x 120 ml</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>7</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O216" s="2" t="n"/>
+      <c r="P216" s="2" t="n"/>
+      <c r="Q216" s="3" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>25</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Bon Gelati Bâtonnets glacés vanille, chocolat blanc, amandes, surgelés, 6 x 100 ml</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>7</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O217" s="2" t="n"/>
+      <c r="P217" s="2" t="n"/>
+      <c r="Q217" s="3" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>25</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Gelatelli Bâtonnets glacés à la pistache, surgelés, 4 x 80 ml</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>7</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N218" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O218" s="2" t="n"/>
+      <c r="P218" s="2" t="n"/>
+      <c r="Q218" s="3" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>25</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Gelatelli Mini Mix fruits, surgelés, 12 x 50 ml</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>7</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N219" s="2" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="O219" s="2" t="n"/>
+      <c r="P219" s="2" t="n"/>
+      <c r="Q219" s="3" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>26</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Allini Secco, Rosato ou Bianco, 20 cl</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>7</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="N220" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O220" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P220" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q220" s="3" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>26</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Allini Prosecco DOC, 37,5 cl</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>7</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Italie – Vénétie</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O221" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P221" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q221" s="3" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>26</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Italiamo Escargots pizza, diverses sortes, 270 g</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>7</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="O222" s="2" t="n"/>
+      <c r="P222" s="2" t="n"/>
+      <c r="Q222" s="3" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>26</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Italiamo Garniture fraîche pour bruschetta, diverses sortes, 150 g</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>2</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O223" s="2" t="n"/>
+      <c r="P223" s="2" t="n"/>
+      <c r="Q223" s="3" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>26</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Italiamo Cantuccini à l'orange, 200 g</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>7</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O224" s="2" t="n"/>
+      <c r="P224" s="2" t="n"/>
+      <c r="Q224" s="3" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>26</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Italiamo Pain en tranches pour bruschetta, 500 g</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>3</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="N225" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O225" s="2" t="n"/>
+      <c r="P225" s="2" t="n"/>
+      <c r="Q225" s="3" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>28</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Italiamo Pizza prosciutto mozzarella, surgelée, 400 g</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>7</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N226" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="O226" s="2" t="n"/>
+      <c r="P226" s="2" t="n"/>
+      <c r="Q226" s="3" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>28</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Dr. Oetker Pizza Ristorante, diverses sortes, 355 g – 320 g</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>7</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N227" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="O227" s="2" t="n"/>
+      <c r="P227" s="2" t="n"/>
+      <c r="Q227" s="3" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>28</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Italiamo Pain galette (Piada Sfogliata), 390 g</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>3</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="N228" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O228" s="2" t="n"/>
+      <c r="P228" s="2" t="n"/>
+      <c r="Q228" s="3" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>28</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Italiamo Tomates cerises italiennes au jus de tomate, 250 g</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>2</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O229" s="2" t="n"/>
+      <c r="P229" s="2" t="n"/>
+      <c r="Q229" s="3" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>28</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Italiamo Sauces pour pâtes, diverses sortes, 350 g</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>7</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O230" s="2" t="n"/>
+      <c r="P230" s="2" t="n"/>
+      <c r="Q230" s="3" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>28</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Italiamo Provolone, dolce ou piccante, 300 g</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>4</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="N231" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="O231" s="2" t="n"/>
+      <c r="P231" s="2" t="n"/>
+      <c r="Q231" s="3" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>29</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Italiamo Sfogliatine Glassate, 200 g</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>7</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Avec Lidl Plus</t>
+        </is>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O232" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P232" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q232" s="3" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>29</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Italiamo Biscuits sablés au lait et au miel, 350 g</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>7</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O233" s="2" t="n"/>
+      <c r="P233" s="2" t="n"/>
+      <c r="Q233" s="3" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>29</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Italiamo Croissants fourrés à la crème, pistache ou tiramisu, 5 x 48 g</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>7</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N234" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O234" s="2" t="n"/>
+      <c r="P234" s="2" t="n"/>
+      <c r="Q234" s="3" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>29</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Italiamo Gâteau amaretto ou limoncello, surgelé, 700 g / 830 g</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>7</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N235" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="O235" s="2" t="n"/>
+      <c r="P235" s="2" t="n"/>
+      <c r="Q235" s="3" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>29</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Gelatelli Lollies Praliné, diverses sortes, surgelés, 4 x 70 ml</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>7</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N236" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O236" s="2" t="n"/>
+      <c r="P236" s="2" t="n"/>
+      <c r="Q236" s="3" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>29</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Gelatelli Glace à l'italienne, diverses sortes, surgelée, 500 ml</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>7</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N237" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O237" s="2" t="n"/>
+      <c r="P237" s="2" t="n"/>
+      <c r="Q237" s="3" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>29</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Flaureo Prosecco Rosé Millesimato ou Grillo Spumante Brut, 75 cl</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>7</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N238" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="O238" s="2" t="n"/>
+      <c r="P238" s="2" t="n"/>
+      <c r="Q238" s="3" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>31</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Fantini Farnese Edizione Cinque Autoctoni, 75 cl</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>7</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="O239" s="2" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="P239" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="Q239" s="3" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>31</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Allini Moscato Spumante Dolce, 75 cl</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>7</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O240" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P240" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q240" s="3" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>31</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Più Secco, 75 cl</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>7</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O241" s="2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P241" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q241" s="3" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>31</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Maestro de Pigo Primitivo di Manduria DOC, 75 cl</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>7</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Italie – Pouilles</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
+      <c r="N242" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="O242" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="P242" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q242" s="3" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>31</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Aperol Bitter, 11% vol., 1 l</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>7</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="O243" s="2" t="n"/>
+      <c r="P243" s="2" t="n"/>
+      <c r="Q243" s="3" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>31</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Aperol Spritz, 9% vol., 3 x 20 cl</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>7</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N244" s="2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="O244" s="2" t="n"/>
+      <c r="P244" s="2" t="n"/>
+      <c r="Q244" s="3" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>31</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Ponte Giulio Orvieto Classico, 75 cl</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>7</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="N245" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="O245" s="2" t="n"/>
+      <c r="P245" s="2" t="n"/>
+      <c r="Q245" s="3" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>41</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Salami gourmet, diverses sortes, 250 g</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>5</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="O246" s="2" t="n"/>
+      <c r="P246" s="2" t="n"/>
+      <c r="Q246" s="3" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>41</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Filet de canard de Barbarie, mariné ou mariné à la provençale, surgelé, 400 g</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>5</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N247" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="O247" s="2" t="n"/>
+      <c r="P247" s="2" t="n"/>
+      <c r="Q247" s="3" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>41</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Coulommiers de Caractère, 350 g</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>4</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="N248" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="O248" s="2" t="n"/>
+      <c r="P248" s="2" t="n"/>
+      <c r="Q248" s="3" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>41</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Escargots farcis, surgelés, 67 g</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>5</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="N249" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O249" s="2" t="n"/>
+      <c r="P249" s="2" t="n"/>
+      <c r="Q249" s="3" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>41</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Gratin de pommes de terre avec reblochon, surgelé, 360 g</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>3</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="N250" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="O250" s="2" t="n"/>
+      <c r="P250" s="2" t="n"/>
+      <c r="Q250" s="3" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
         <v>43</v>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Evian Eau minérale plate, 6 x 1,5 l</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-50% en pack de 6</t>
+        </is>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="O251" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="P251" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q251" s="3" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>43</v>
+      </c>
+      <c r="C252" t="inlineStr">
         <is>
           <t>Côtes du Rhône AOP 2021, 75 cl</t>
         </is>
       </c>
-      <c r="D202" t="n">
-        <v>7</v>
-      </c>
-      <c r="E202" t="inlineStr">
+      <c r="D252" t="n">
+        <v>7</v>
+      </c>
+      <c r="E252" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G252" t="inlineStr">
         <is>
           <t>France – Rhône</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H252" t="inlineStr">
         <is>
           <t>AOP</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K252" t="inlineStr">
         <is>
           <t>-24%</t>
         </is>
       </c>
-      <c r="N202" s="2" t="n">
+      <c r="N252" s="2" t="n">
         <v>3.29</v>
       </c>
-      <c r="O202" s="2" t="n">
+      <c r="O252" s="2" t="n">
         <v>2.49</v>
       </c>
-      <c r="P202" s="2" t="n">
+      <c r="P252" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q202" s="3" t="n">
+      <c r="Q252" s="3" t="n">
         <v>24.3</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>43</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Duc de Coeur En-cas au maïs jambon-fromage, 75 g</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>7</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N253" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O253" s="2" t="n"/>
+      <c r="P253" s="2" t="n"/>
+      <c r="Q253" s="3" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>43</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Biscuits au beurre fourrés, diverses sortes, 100 g</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>7</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N254" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O254" s="2" t="n"/>
+      <c r="P254" s="2" t="n"/>
+      <c r="Q254" s="3" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>43</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Pâte à tartiner sucrée, diverses sortes, 200 g</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>7</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N255" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O255" s="2" t="n"/>
+      <c r="P255" s="2" t="n"/>
+      <c r="Q255" s="3" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>43</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Spécialités de dessert, profiteroles ou crème caramel, 450 g</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>7</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="O256" s="2" t="n"/>
+      <c r="P256" s="2" t="n"/>
+      <c r="Q256" s="3" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>43</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Crème brûlée, 2 x 100 g</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>7</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O257" s="2" t="n"/>
+      <c r="P257" s="2" t="n"/>
+      <c r="Q257" s="3" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>43</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Duc de Coeur Macarons glacés, surgelés, 6 x 20 g</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>7</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Rainforest Alliance</t>
+        </is>
+      </c>
+      <c r="N258" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="O258" s="2" t="n"/>
+      <c r="P258" s="2" t="n"/>
+      <c r="Q258" s="3" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Semaine 23_Lidl.pdf</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>43</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Bordeaux Supérieur Barrique AOP 2021, 75 cl</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>7</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>France – Bordeaux</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="O259" s="2" t="n"/>
+      <c r="P259" s="2" t="n"/>
+      <c r="Q259" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q202"/>
+  <autoFilter ref="A1:Q259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/promotions_extraites.xlsx
+++ b/promotions_extraites.xlsx
@@ -3725,11 +3725,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6979,11 +6979,11 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9428,11 +9428,11 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="N202" s="2" t="n">
@@ -10136,11 +10136,11 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="N223" s="2" t="n">
@@ -11014,11 +11014,11 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="N250" s="2" t="n">

--- a/promotions_extraites.xlsx
+++ b/promotions_extraites.xlsx
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4055,11 +4055,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="N79" s="2" t="n">
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="N202" s="2" t="n">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="N230" s="2" t="n">
@@ -10985,11 +10985,11 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="N249" s="2" t="n">

--- a/promotions_extraites.xlsx
+++ b/promotions_extraites.xlsx
@@ -6661,11 +6661,11 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7362,11 +7362,11 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">

--- a/promotions_extraites.xlsx
+++ b/promotions_extraites.xlsx
@@ -437,10 +437,10 @@
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -481,12 +481,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>type_poisson</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>provenance</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -554,15 +554,17 @@
           <t>Mini-pastèques Migros Bio, la pièce</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Espagne</t>
         </is>
@@ -604,15 +606,17 @@
           <t>Émincé de poulet Optigal, 2 x 350 g</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>5</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -654,15 +658,17 @@
           <t>Hamburgers de bœuf Migros, 4 pièces, 500 g</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>5</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -699,12 +705,14 @@
           <t>Tous les fruits à coque Party, y compris les mélanges (p. ex. pistaches grillées et salées, 500 g)</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>7</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -744,12 +752,14 @@
           <t>Tout l'assortiment de barres de céréales et d'en-cas, Farmer (p. ex. barres de céréales à la pomme Soft Choc, 288 g)</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>7</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -794,15 +804,17 @@
           <t>Cerises Migros Bio, la barquette de 500 g</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>2</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Suisse/Italie/Espagne</t>
         </is>
@@ -844,15 +856,17 @@
           <t>Tomates cerises en grappe, la barquette de 500 g</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>2</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+          <t>2.2 Légumes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -889,15 +903,17 @@
           <t>Concombres, la pièce</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+          <t>2.2 Légumes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Suisse/Pays-Bas</t>
         </is>
@@ -939,15 +955,17 @@
           <t>Pêches jaunes, le kg</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Espagne/Italie/France</t>
         </is>
@@ -984,15 +1002,17 @@
           <t>Poivrons assortis, le sachet de 500 g</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>2</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+          <t>2.2 Légumes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Espagne/Pays-Bas</t>
         </is>
@@ -1029,15 +1049,17 @@
           <t>Portobello Migros Bio, la barquette de 110 g</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>2</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+          <t>2.2 Légumes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Pays-Bas</t>
         </is>
@@ -1079,15 +1101,17 @@
           <t>Melon Brodé, la pièce</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
@@ -1124,15 +1148,17 @@
           <t>Tomates Rose de Berne, le kg</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>2</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+          <t>2.2 Légumes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -1169,12 +1195,14 @@
           <t>Salade feuille de chêne verte «De la région.», la pièce</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>2</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.2 Légumes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1214,15 +1242,17 @@
           <t>Viande hachée de bœuf Migros, 700 g</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>5</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -1259,15 +1289,17 @@
           <t>Filet d'agneau Migros, les 100 g</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>5</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Nouvelle-Zélande/Australie</t>
         </is>
@@ -1304,15 +1336,17 @@
           <t>Entrecôtes de bœuf Black Angus Migros, 2 pièces, les 100 g</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>5</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
@@ -1349,12 +1383,14 @@
           <t>Steaks de porc bûcheron marinés IP-SUISSE, les 100 g</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>5</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.1 Viande hors charcuterie</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1394,12 +1430,14 @@
           <t>Rumpsteak de bœuf «De la région.», les 100 g</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>5</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.1 Viande hors charcuterie</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1439,12 +1477,14 @@
           <t>Poulet entier Optigal, IP-SUISSE, nature ou épicé (p. ex. nature, le kg)</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>5</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.1 Viande hors charcuterie</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1484,15 +1524,17 @@
           <t>Ailes de poulet Optigal, nature ou épicées, le kg</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>5</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -1529,12 +1571,14 @@
           <t>Fricassées de porc IP-SUISSE, les 100 g</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>5</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.1 Viande hors charcuterie</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1574,12 +1618,14 @@
           <t>Saucisse à rôtir de porc «De la région.», les 100 g</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>5</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1619,12 +1665,14 @@
           <t>Poulet Crispy Don Pollo, surgelé, 1,4 kg</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>7</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1659,15 +1707,17 @@
           <t>Plateau de chipolatas et merguez Migros, les 100 g</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>5</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+          <t>5.2 Charcuterie</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Suisse/France/Irlande</t>
         </is>
@@ -1704,12 +1754,14 @@
           <t>Lard à griller IP-SUISSE, les 100 g</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>5</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1749,15 +1801,17 @@
           <t>Party sticks Malbuner, 3 x 40 g</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>5</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+          <t>5.2 Charcuterie</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -1799,15 +1853,17 @@
           <t>Brochettes de cheval à l'ail Migros, 4 pièces, les 100 g</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>5</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Espagne</t>
         </is>
@@ -1844,15 +1900,17 @@
           <t>Prosciutto crudo Emilia Romagna Beretta, 125 g</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>5</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+          <t>5.2 Charcuterie</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
@@ -1889,12 +1947,14 @@
           <t>Jambon Gourmet IP-SUISSE, 130 g</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>5</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1934,15 +1994,17 @@
           <t>Viande séchée des Grisons Spécialité Suisse, IGP, 120 g</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>5</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+          <t>5.2 Charcuterie</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -1984,15 +2046,17 @@
           <t>Saucisse de Vienne M-Classic, 5 x 4 pièces, 5 x 200 g</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>5</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+          <t>5.2 Charcuterie</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -2034,15 +2098,17 @@
           <t>Steaks de cuisse de poulet Migros, les 100 g</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>5</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -2073,22 +2139,24 @@
           <t>Saumon sauvage sockeye Migros, MSC, 280 g</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>5</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.3 Poisson</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>Pacifique Nord-Est (zone de pêche)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>sauvage</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Pacifique Nord-Est (zone de pêche)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2128,22 +2196,24 @@
           <t>Crevettes blanchies et décortiquées M-Classic, ASC, 450 g</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>5</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.3 Poisson</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Équateur</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>élevage</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Équateur</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2183,22 +2253,24 @@
           <t>Poissons frais en barquette de cuisson Migros (p. ex. filet de saumon ASC, 400 g)</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>5</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.3 Poisson</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>élevage</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Norvège</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2238,22 +2310,24 @@
           <t>Dorade royale Migros Bio, les 100 g</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>5</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.3 Poisson</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Croatie</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>élevage</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Croatie</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2293,22 +2367,24 @@
           <t>Filets de saumon sans peau M-Classic, ASC, 380 g</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>5</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.3 Poisson</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>élevage</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Norvège</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2348,12 +2424,14 @@
           <t>Le Gruyère surchoix AOP, env. 280 g, les 100 g</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>4</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2393,12 +2471,14 @@
           <t>Grana Padano Da Emilio (p. ex. râpé, 120 g)</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>4</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2433,12 +2513,14 @@
           <t>Tête de Moine en rosettes AOP, 2 x 120 g</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>4</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2483,12 +2565,14 @@
           <t>Fromage à griller Happily Baer, Fromella Provençale ou Tomme Original (p. ex. Fromella, 2 x 220 g)</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>4</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2533,12 +2617,14 @@
           <t>Fromage doux à la crème Emmi Luzerner, env. 280 g, les 100 g</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>4</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2573,12 +2659,14 @@
           <t>Emmental doux, env. 250 g, les 100 g</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>4</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2613,12 +2701,14 @@
           <t>Le Chèvre Sanglé «De la région.», 180 g</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>4</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2658,12 +2748,14 @@
           <t>Raclette en tranches pour burger Emmi, 150 g</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>4</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2698,12 +2790,14 @@
           <t>Beurre de cuisine M-Classic, 4 x 250 g</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>6</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.1 Beurre</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2743,12 +2837,14 @@
           <t>Tout l'assortiment Gerber (p. ex. toast au fromage fondu, sans lactose, 10 tranches, 200 g)</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>4</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2783,12 +2879,14 @@
           <t>Yogourts Mocca La Semeuse, bio, Fairtrade, 4 x 150 g</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>4</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.2 Yogourts et séré aromatisés</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2838,15 +2936,17 @@
           <t>Œufs suisses d'élevage en plein air Migros Bio, 6 x 53 g+</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>5</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+          <t>5.4 Œufs</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -2898,12 +2998,14 @@
           <t>Boule de mozzarella Alfredo, 150 g</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>4</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -2932,12 +3034,14 @@
           <t>Demi-crème Valflora en bombe, IP-SUISSE, 2 x 250 ml</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>6</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.3 Crème</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2982,12 +3086,14 @@
           <t>Gala Nature Emmi, 80 g</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>4</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3027,12 +3133,14 @@
           <t>Tartare Ail &amp; fines herbes High Protein, 150 g</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>4</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3066,12 +3174,14 @@
           <t>Philadelphia, nature, balance ou aux herbes (p. ex. nature, 2 x 200 g)</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>4</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3111,12 +3221,14 @@
           <t>Yogourts Pur Emmi, framboise ou fraise, 4 x 150 g</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>4</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.2 Yogourts et séré aromatisés</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3156,12 +3268,14 @@
           <t>Yogourt nature Yogos, 4 x 180 g</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>4</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.3 Yogourts et séré nature</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3201,12 +3315,14 @@
           <t>Plateau apéro «De la région.», 180 g</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>4</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3246,12 +3362,14 @@
           <t>Yogourts et boissons au kéfir Emmi (p. ex. yogourt à la fraise, 150 g)</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>4</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.2 Yogourts et séré aromatisés</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3286,12 +3404,14 @@
           <t>Milk Drink good day Emmi, sans lactose, 1 litre</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>4</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.4 Boissons lactées sans sucre ajoutés</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3336,12 +3456,14 @@
           <t>Yogi Drink Emmi, framboise ou mocca, 3 x 200 ml</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>7</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3381,12 +3503,14 @@
           <t>Benecol Emmi, myrtille, fraise ou framboise sans sucre cristallisé (p. ex. myrtille, 12 x 65 ml)</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>4</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.5 Autres</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3426,12 +3550,14 @@
           <t>Yogourts à boire Aktifit Emmi, fraise, pêche ou Globi, 12 x 65 ml</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>7</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3471,12 +3597,14 @@
           <t>Birchermuesli Anna's Best, 185 g</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>7</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3510,12 +3638,14 @@
           <t>Caffè Latte Emmi, macchiato, balance ou double zero (p. ex. macchiato, 3 x 230 ml)</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>7</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3555,12 +3685,14 @@
           <t>Tous les repas à boire I'm your meal et Energy Milk, Emmi (p. ex. I'm your meal, goût chocolat, 500 ml)</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>7</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3600,12 +3732,14 @@
           <t>Birchermuesli Migros Bio, 185 g</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>7</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3644,12 +3778,14 @@
           <t>Toutes les salades et pâtes à tartiner, Neni (excepté Daily by Neni) (p. ex. houmous pois chiches et huile d'olive, végane, 200 g)</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>7</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3684,12 +3820,14 @@
           <t>Toutes les tourtes non réfrigérées (p. ex. tourte de Linz Petit Bonheur, 400 g)</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>7</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3724,12 +3862,14 @@
           <t>Tous les plats tout prêts Anna's Best (p. ex. riz casimir avec poulet et fruits, 400 g)</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>7</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -3769,12 +3909,14 @@
           <t>Tous les buns pour hamburger Migros (p. ex. Burger Buns, précoupés, 6 pièces, 300 g)</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>3</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1 Pains</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -3809,12 +3951,14 @@
           <t>Escalopes aux légumes et pommes de terre ou Crispy Tofu, Migros Bio (p. ex. escalopes, 2 x 180 g)</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>7</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3864,12 +4008,14 @@
           <t>Gazpacho Alvalle, 1 litre ou 500 ml (p. ex. 1 litre)</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>2</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.2 Légumes</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3909,12 +4055,14 @@
           <t>Tous les petits pains rustiques, pointus et Vital en vrac (p. ex. petit pain rustique, 85 g)</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>3</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1 Pains</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3954,12 +4102,14 @@
           <t>Tout l'assortiment Pancho Villa (p. ex. tortillas Flour big, 6 pièces, 350 g)</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>3</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1 Pains</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3999,15 +4149,17 @@
           <t>Avocats Migros Bio, la pièce</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>2</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Pérou</t>
         </is>
@@ -4054,15 +4206,17 @@
           <t>Escalopes de poulet pané Migros, les 100 g</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>7</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Brésil</t>
         </is>
@@ -4099,12 +4253,14 @@
           <t>BrokenTaco Diablo Crema, Sweet Taco Topping ou Green Sriracha, 200 g</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>7</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6 Sauces et condiments</t>
         </is>
       </c>
       <c r="N79" s="2" t="n">
@@ -4128,12 +4284,14 @@
           <t>Haribo Pixels acidulés, 1,2 kg</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>7</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4162,15 +4320,17 @@
           <t>Olives en sachet Migros (excepté Demeter et Alnatura) (p. ex. olives espagnoles Hojiblanca dénoyautées, 150 g)</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>7</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+          <t>7.2 Snacks salés</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Espagne</t>
         </is>
@@ -4212,12 +4372,14 @@
           <t>Croissants au jambon Happy Hour, M-Classic, surgelé, 24 pièces, 1008 g</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>7</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4252,12 +4414,14 @@
           <t>Pepsi, Regular, Zero, Cherry Zero et sans caféine (p. ex. Regular, 6 x 1,5 litre)</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>7</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4297,12 +4461,14 @@
           <t>Biscuits pour l'apéritif Party, Pizza Crackers, Crackers ou Sticks (p. ex. pizza crackers, 450 g)</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>7</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4337,15 +4503,17 @@
           <t>Salsiccia Ticinese Rapelli, 480 g</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>5</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+          <t>5.2 Charcuterie</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -4382,12 +4550,14 @@
           <t>Chips Zweifel, paprika ou nature, 2 x 175 g</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>7</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4427,12 +4597,14 @@
           <t>Snacketti Zweifel, Paprika Shells, Dancer Cream ou Bacon Strips Flavour, XXL Big Pack, 225 g</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>7</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4467,12 +4639,14 @@
           <t>Eau minérale Aproz, diverses variétés (p. ex. gazéifiée, 6 x 1,5 litre)</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>1</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1. Boissons</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1 Eau nature</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4512,12 +4686,14 @@
           <t>Schweppes, diverses variétés (p. ex. Bitter Lemon, 6 x 500 ml)</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>7</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4557,12 +4733,14 @@
           <t>Red Bull Sugarfree ou Zero, 6 x 250 ml</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>7</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4602,12 +4780,14 @@
           <t>Capri-Sun Multivitamin, Multivitamin Zero, Monster ou Mystic Dragon, 10 x 200 ml</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>7</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4647,12 +4827,14 @@
           <t>Tous les sirops en bouteilles PET (p. ex. framboise, 750 ml)</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>7</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4687,12 +4869,14 @@
           <t>Red Bull Summer Edition Sugarfree Sudachi-Lime, 250 ml</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>7</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4726,12 +4910,14 @@
           <t>Volvic Essence agrumes-romarin (p. ex. 6 x 750 ml)</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>1</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1. Boissons</t>
+        </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2 Eau aromatisée</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -4765,12 +4951,14 @@
           <t>Eau minérale Evian Sparkling, 500 ml</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>1</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1. Boissons</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1 Eau nature</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -4804,12 +4992,14 @@
           <t>Lillet Blanc, sans alcool, 750 ml</t>
         </is>
       </c>
-      <c r="D96" t="n">
-        <v>7</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -4843,12 +5033,14 @@
           <t>Monster Bad Apple Energy et Juice, 500 ml</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>7</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4882,12 +5074,14 @@
           <t>Lamate Mango Migros, 330 ml</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>7</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4921,12 +5115,14 @@
           <t>Fanta Orange (p. ex. 6 x 330 ml)</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>7</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4960,12 +5156,14 @@
           <t>Spezi Paulaner, 330 ml</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>7</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4999,12 +5197,14 @@
           <t>Freixenet Solare, 750 ml</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>7</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4 Boissons alcoolisées</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5038,12 +5238,14 @@
           <t>Bilz Chill &amp; Relax, sans alcool, White Peach &amp; Jasmine, 6 x 330 ml</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>7</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5077,12 +5279,14 @@
           <t>Biotta Well Fibres bio, 500 ml</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>1</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1. Boissons</t>
+        </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3 Jus de fruits 100% fruits</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5121,12 +5325,14 @@
           <t>Coca-Cola zéro caféine et zéro sucre (p. ex. 1,5 litre)</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>7</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5160,12 +5366,14 @@
           <t>Matcha Carpe Diem, 500 ml</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>7</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5199,12 +5407,14 @@
           <t>Huile de tournesol M-Classic, 1 litre</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>6</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.2 Huile</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5244,12 +5454,14 @@
           <t>Pâtes Migros Bio, réfrigérées, tortelloni ricotta e spinaci ou fettuccine aux œufs (p. ex. tortelloni, 3 x 250 g)</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>7</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5299,12 +5511,14 @@
           <t>Pizzas au four à bois Anna's Best, réfrigérées, mini Prosciutto ou Prosciutto &amp; mascarpone (p. ex. mini Prosciutto, 3 x 210 g)</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>7</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -5344,12 +5558,14 @@
           <t>Miel de fleurs Fairtrade, crémeux ou liquide (p. ex. crémeux, 2 x 550 g)</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>7</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5394,12 +5610,14 @@
           <t>Tomates concassées Longobardi, 6 x 400 g</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>2</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.2 Légumes</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5439,12 +5657,14 @@
           <t>Tranches d'ananas Sun Queen, lot de 6 (p. ex. 6 x 140 g)</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>2</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.1 Fruits</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5489,12 +5709,14 @@
           <t>Crunchy Cream Ovomaltine, 860 g</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>7</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -5529,12 +5751,14 @@
           <t>Riz long grain parboiled Migros, 1 kg</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v>3</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.2 Riz</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -5563,12 +5787,14 @@
           <t>Pizzas La Trattoria, surgelées, mozzarella, prosciutto ou tonno (p. ex. mozzarella, 3 x 330 g)</t>
         </is>
       </c>
-      <c r="D114" t="n">
-        <v>7</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -5608,12 +5834,14 @@
           <t>Tous les müeslis Farmer (p. ex. baies des bois Classic, 500 g)</t>
         </is>
       </c>
-      <c r="D115" t="n">
-        <v>7</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -5653,12 +5881,14 @@
           <t>Tous les cafés La Semeuse (p. ex. mocca surfin, moulu)</t>
         </is>
       </c>
-      <c r="D116" t="n">
-        <v>1</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1. Boissons</t>
+        </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4 Autres</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -5698,12 +5928,14 @@
           <t>Lait de coco Thai Kitchen, classique ou bio (p. ex. classique, 2 x 500 ml)</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v>6</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5 Autres</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -5743,12 +5975,14 @@
           <t>Sucre fin cristallisé Cristal M-Classic, IP-SUISSE, 4 x 1 kg</t>
         </is>
       </c>
-      <c r="D118" t="n">
-        <v>7</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5793,12 +6027,14 @@
           <t>Cafés instantanés Cafino (excepté bio), Classic et Voncoré (p. ex. Classic, 550 g)</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>1</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1. Boissons</t>
+        </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4 Autres</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5843,12 +6079,14 @@
           <t>Branches Frey, Milk ou Dark, 50 x 27 g (p. ex. Milk)</t>
         </is>
       </c>
-      <c r="D120" t="n">
-        <v>7</v>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5888,12 +6126,14 @@
           <t>Plaques de chocolat Frey assorties, 20 x 100 g</t>
         </is>
       </c>
-      <c r="D121" t="n">
-        <v>7</v>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5938,12 +6178,14 @@
           <t>Chocolat Ovomaltine, diverses variétés (p. ex. Ovo rocks, 2 x 120 g)</t>
         </is>
       </c>
-      <c r="D122" t="n">
-        <v>7</v>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -5983,12 +6225,14 @@
           <t>Boules de chocolat au lait Lindor Lindt, 3 x 200 g</t>
         </is>
       </c>
-      <c r="D123" t="n">
-        <v>7</v>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -6028,12 +6272,14 @@
           <t>Kägi Fret en sachet, Classic, noisette ou orange, 250 g</t>
         </is>
       </c>
-      <c r="D124" t="n">
-        <v>7</v>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -6062,12 +6308,14 @@
           <t>Bâtonnets de glace Choquello Praliné, Exotic Mini ou Exotic, surgelés (p. ex. Choquello Praliné, 8 x 82 ml)</t>
         </is>
       </c>
-      <c r="D125" t="n">
-        <v>7</v>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6112,15 +6360,17 @@
           <t>Fraises, la barquette de 500 g (p. ex. Suisse)</t>
         </is>
       </c>
-      <c r="D126" t="n">
-        <v>2</v>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Suisse ou Pays-Bas</t>
         </is>
@@ -6162,12 +6412,14 @@
           <t>Tous les sandwiches Migros et les toasts American Favorites, IP-SUISSE</t>
         </is>
       </c>
-      <c r="D127" t="n">
-        <v>3</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1 Pains</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6204,12 +6456,14 @@
           <t>Steaks de filet de porc marinés IP-SUISSE, les 100 g</t>
         </is>
       </c>
-      <c r="D128" t="n">
-        <v>5</v>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.1 Viande hors charcuterie</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6254,15 +6508,17 @@
           <t>Fraises, 500 g</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v>2</v>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -6304,12 +6560,14 @@
           <t>Fisher's Choice Filets de saumon bio</t>
         </is>
       </c>
-      <c r="D130" t="n">
-        <v>5</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.3 Poisson</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6349,12 +6607,14 @@
           <t>Malvoisie AOC</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>7</v>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4 Boissons alcoolisées</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6399,12 +6659,14 @@
           <t>Qualité Suisse Viande hachée mélangée allégée</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>5</v>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.1 Viande hors charcuterie</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6443,12 +6705,14 @@
           <t>Allini Secco</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v>7</v>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4 Boissons alcoolisées</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -6483,12 +6747,14 @@
           <t>Duc de Coeur Filet de poitrine de canard de Barbarie, surgelé</t>
         </is>
       </c>
-      <c r="D134" t="n">
-        <v>5</v>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.1 Viande hors charcuterie</t>
         </is>
       </c>
       <c r="N134" s="2" t="n">
@@ -6512,15 +6778,17 @@
           <t>Qualité Suisse Plat de grillades de fête, 550 g</t>
         </is>
       </c>
-      <c r="D135" t="n">
-        <v>5</v>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -6561,15 +6829,17 @@
           <t>Nautica Saumon fumé GGN, 170 g</t>
         </is>
       </c>
-      <c r="D136" t="n">
-        <v>5</v>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
+          <t>5.3 Poisson</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Norvège</t>
         </is>
@@ -6605,12 +6875,14 @@
           <t>Qualité Suisse Baguette rustique Terra Natura, 410 g</t>
         </is>
       </c>
-      <c r="D137" t="n">
-        <v>3</v>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1 Pains</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6660,12 +6932,14 @@
           <t>Ocean Sea Bâtonnets de poisson MSC, surgelés, 15 pièces, 450 g</t>
         </is>
       </c>
-      <c r="D138" t="n">
-        <v>7</v>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6705,15 +6979,17 @@
           <t>Qualité Suisse Escalopes de filet de porc ultra fines, pack de 2 XXL, 2 x 380 g</t>
         </is>
       </c>
-      <c r="D139" t="n">
-        <v>5</v>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -6754,15 +7030,17 @@
           <t>Mont-sur-Rolle La Côte AOC, 75 cl</t>
         </is>
       </c>
-      <c r="D140" t="n">
-        <v>7</v>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Suisse – Vaud</t>
         </is>
@@ -6809,15 +7087,17 @@
           <t>Cœurs de laitues pommées suisses, 2 pièces</t>
         </is>
       </c>
-      <c r="D141" t="n">
-        <v>2</v>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
+          <t>2.2 Légumes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -6859,12 +7139,14 @@
           <t>Dulano Selection Bâtonnets de salami, classiques ou piquants, 100 g</t>
         </is>
       </c>
-      <c r="D142" t="n">
-        <v>5</v>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -6899,12 +7181,14 @@
           <t>Freeway Mate, diverses sortes, 33 cl</t>
         </is>
       </c>
-      <c r="D143" t="n">
-        <v>7</v>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -6944,12 +7228,14 @@
           <t>Sprite, pack de 24, 24 x 33 cl</t>
         </is>
       </c>
-      <c r="D144" t="n">
-        <v>7</v>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -6978,12 +7264,14 @@
           <t>Chef Select Bowl de salade, diverses sortes, 300 g</t>
         </is>
       </c>
-      <c r="D145" t="n">
-        <v>7</v>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -7018,15 +7306,17 @@
           <t>Abricots, le kg</t>
         </is>
       </c>
-      <c r="D146" t="n">
-        <v>2</v>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Espagne, Italie</t>
         </is>
@@ -7068,15 +7358,17 @@
           <t>Fraises, 500 g</t>
         </is>
       </c>
-      <c r="D147" t="n">
-        <v>2</v>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -7118,15 +7410,17 @@
           <t>Pastèque, le kg</t>
         </is>
       </c>
-      <c r="D148" t="n">
-        <v>2</v>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
+          <t>2.1 Fruits</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Espagne, Italie</t>
         </is>
@@ -7163,12 +7457,14 @@
           <t>Feuilleté carbonara, 119 g</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>7</v>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -7197,12 +7493,14 @@
           <t>Croissant jambon-fromage, 3 x 95 g</t>
         </is>
       </c>
-      <c r="D150" t="n">
-        <v>7</v>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -7237,12 +7535,14 @@
           <t>Chausson à la cannelle, 113 g</t>
         </is>
       </c>
-      <c r="D151" t="n">
-        <v>7</v>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -7271,12 +7571,14 @@
           <t>Croissant fourré au praliné noisette, 85 g</t>
         </is>
       </c>
-      <c r="D152" t="n">
-        <v>7</v>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -7311,12 +7613,14 @@
           <t>Qualité Suisse Couronne de Sils, 360 g</t>
         </is>
       </c>
-      <c r="D153" t="n">
-        <v>3</v>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1 Pains</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7361,15 +7665,17 @@
           <t>Fisher's Choice Filets de silure requin croustillants ASC XXL, 500 g</t>
         </is>
       </c>
-      <c r="D154" t="n">
-        <v>7</v>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
@@ -7405,15 +7711,17 @@
           <t>Fisher's Choice Filets de saumon bio, avec peau, 3 x 125 g</t>
         </is>
       </c>
-      <c r="D155" t="n">
-        <v>5</v>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
+          <t>5.3 Poisson</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
         <is>
           <t>Norvège</t>
         </is>
@@ -7455,15 +7763,17 @@
           <t>Qualité Suisse Viande hachée mélangée allégée, pack de 2, 2 x 370 g</t>
         </is>
       </c>
-      <c r="D156" t="n">
-        <v>5</v>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -7504,15 +7814,17 @@
           <t>Deluxe Filet d'agneau mariné, 100 g</t>
         </is>
       </c>
-      <c r="D157" t="n">
-        <v>5</v>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
         <is>
           <t>Irlande</t>
         </is>
@@ -7543,15 +7855,17 @@
           <t>Qualité Suisse Steak de cou de porc, assaisonné, 800 g</t>
         </is>
       </c>
-      <c r="D158" t="n">
-        <v>5</v>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -7592,15 +7906,17 @@
           <t>Qualité Suisse Brochettes flambeau farcies, 400 g</t>
         </is>
       </c>
-      <c r="D159" t="n">
-        <v>5</v>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
@@ -7652,15 +7968,17 @@
           <t>Deluxe Steak de bœuf Striploin Irish Angus, 250 g</t>
         </is>
       </c>
-      <c r="D160" t="n">
-        <v>5</v>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>Irlande</t>
         </is>
@@ -7686,15 +8004,17 @@
           <t>Deluxe Steak de contre-filet Irish Angus, 250 g</t>
         </is>
       </c>
-      <c r="D161" t="n">
-        <v>5</v>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
         <is>
           <t>Irlande</t>
         </is>
@@ -7720,15 +8040,17 @@
           <t>Deluxe Steak de filet Irish Angus, 200 g</t>
         </is>
       </c>
-      <c r="D162" t="n">
-        <v>5</v>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
         <is>
           <t>Irlande</t>
         </is>
@@ -7754,15 +8076,17 @@
           <t>Deluxe Steak de bœuf ribeye Irish Angus, 250 g</t>
         </is>
       </c>
-      <c r="D163" t="n">
-        <v>5</v>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
+          <t>5.1 Viande hors charcuterie</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
         <is>
           <t>Irlande</t>
         </is>
@@ -7788,15 +8112,17 @@
           <t>Gamellón Crianza, 75 cl</t>
         </is>
       </c>
-      <c r="D164" t="n">
-        <v>7</v>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
         <is>
           <t>Espagne – Murcia</t>
         </is>
@@ -7833,15 +8159,17 @@
           <t>Monte Plogar Cariñena Gran Reserva DO, 75 cl</t>
         </is>
       </c>
-      <c r="D165" t="n">
-        <v>7</v>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
         <is>
           <t>Espagne – Aragon</t>
         </is>
@@ -7872,15 +8200,17 @@
           <t>Corte alle Mura Chianti Riserva, 75 cl</t>
         </is>
       </c>
-      <c r="D166" t="n">
-        <v>7</v>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>Italie – Toscane</t>
         </is>
@@ -7906,12 +8236,14 @@
           <t>Qualité Suisse Poitrine de dinde en tranches, barbecue ou paprika, 120 g</t>
         </is>
       </c>
-      <c r="D167" t="n">
-        <v>5</v>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7961,12 +8293,14 @@
           <t>Ocean Sea Pointes de saumon, sans peau, surgelées, 455 g</t>
         </is>
       </c>
-      <c r="D168" t="n">
-        <v>5</v>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.3 Poisson</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8011,12 +8345,14 @@
           <t>Qualité Suisse Saucisson vaudois, 100 g</t>
         </is>
       </c>
-      <c r="D169" t="n">
-        <v>5</v>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8055,12 +8391,14 @@
           <t>Qualité Suisse Chorizo, doux ou piquant, 150 g</t>
         </is>
       </c>
-      <c r="D170" t="n">
-        <v>5</v>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8105,12 +8443,14 @@
           <t>Qualité Suisse Viande des Grisons, classique, tranches ultra fines, 80 g / 90 g</t>
         </is>
       </c>
-      <c r="D171" t="n">
-        <v>5</v>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8155,12 +8495,14 @@
           <t>Dulano Selection Fuet Extra, 170 g</t>
         </is>
       </c>
-      <c r="D172" t="n">
-        <v>5</v>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -8195,12 +8537,14 @@
           <t>Tartare L'Apéritif, Provence ou Italie, 100 g</t>
         </is>
       </c>
-      <c r="D173" t="n">
-        <v>4</v>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -8229,12 +8573,14 @@
           <t>Vita D'or Margarine végétale, 500 g</t>
         </is>
       </c>
-      <c r="D174" t="n">
-        <v>6</v>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5 Autres</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8274,12 +8620,14 @@
           <t>Vita D'or Huile de colza, 1 l</t>
         </is>
       </c>
-      <c r="D175" t="n">
-        <v>6</v>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.2 Huile</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -8319,12 +8667,14 @@
           <t>Qualité Suisse Lait drink riche en protéines, sans lactose, UHT, 1 l</t>
         </is>
       </c>
-      <c r="D176" t="n">
-        <v>4</v>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.4 Boissons lactées sans sucre ajoutés</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8374,12 +8724,14 @@
           <t>Milbona Boisson riche en protéines, vanille ou chocolat, 350 g</t>
         </is>
       </c>
-      <c r="D177" t="n">
-        <v>7</v>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -8419,12 +8771,14 @@
           <t>Nixe Thon MSC de bonite à ventre rayé à l'huile de tournesol, 156 g</t>
         </is>
       </c>
-      <c r="D178" t="n">
-        <v>5</v>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.3 Poisson</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8464,12 +8818,14 @@
           <t>Alesto Selection Noix de cajou naturelles, 200 g</t>
         </is>
       </c>
-      <c r="D179" t="n">
-        <v>6</v>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.4 Noix et graines</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -8509,12 +8865,14 @@
           <t>Alesto Selection Mélange de fruits à coque, 200 g</t>
         </is>
       </c>
-      <c r="D180" t="n">
-        <v>6</v>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.4 Noix et graines</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -8554,12 +8912,14 @@
           <t>Chef Select Beignets aux pommes, surgelés, 300 g</t>
         </is>
       </c>
-      <c r="D181" t="n">
-        <v>7</v>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -8594,12 +8954,14 @@
           <t>Langnese Magnum White, surgelés, 8 x 100 ml</t>
         </is>
       </c>
-      <c r="D182" t="n">
-        <v>7</v>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -8628,12 +8990,14 @@
           <t>Mövenpick Branche Cailler ou Coco Paradise, surgelés, 900 ml</t>
         </is>
       </c>
-      <c r="D183" t="n">
-        <v>7</v>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -8662,12 +9026,14 @@
           <t>Bilz Panaché sans alcool, 10 x 33 cl</t>
         </is>
       </c>
-      <c r="D184" t="n">
-        <v>7</v>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -8702,12 +9068,14 @@
           <t>Perlenbacher Radler nature sans alcool, 50 cl</t>
         </is>
       </c>
-      <c r="D185" t="n">
-        <v>7</v>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -8742,12 +9110,14 @@
           <t>Gordon's Gin sans alcool, 70 cl</t>
         </is>
       </c>
-      <c r="D186" t="n">
-        <v>7</v>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="N186" s="2" t="n">
@@ -8771,12 +9141,14 @@
           <t>Solevita Boissons Funny Fruit, Cola Lemon ou Tropical, 14 x 20 cl</t>
         </is>
       </c>
-      <c r="D187" t="n">
-        <v>7</v>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -8805,15 +9177,17 @@
           <t>Cave Aliança Casal Mendes Rosé, 75 cl</t>
         </is>
       </c>
-      <c r="D188" t="n">
-        <v>7</v>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
@@ -8850,15 +9224,17 @@
           <t>Torre de Ferro Dão Reserva DOC, 75 cl</t>
         </is>
       </c>
-      <c r="D189" t="n">
-        <v>7</v>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
         <is>
           <t>Portugal – Dão</t>
         </is>
@@ -8900,12 +9276,14 @@
           <t>Somersby Apple Original, 4,5% vol., 4 x 50 cl</t>
         </is>
       </c>
-      <c r="D190" t="n">
-        <v>7</v>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4 Boissons alcoolisées</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -8940,15 +9318,17 @@
           <t>Gamellón Crianza, 75 cl</t>
         </is>
       </c>
-      <c r="D191" t="n">
-        <v>7</v>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
         <is>
           <t>Espagne – Murcia</t>
         </is>
@@ -8985,15 +9365,17 @@
           <t>Malvoisie AOC, 75 cl</t>
         </is>
       </c>
-      <c r="D192" t="n">
-        <v>7</v>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>Suisse – Valais</t>
         </is>
@@ -9040,12 +9422,14 @@
           <t>Deluxe Pralinés façon Dubaï, 120 g (article non disponible)</t>
         </is>
       </c>
-      <c r="D193" t="n">
-        <v>7</v>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -9090,12 +9474,14 @@
           <t>Qualité Suisse Séré maigre sans lactose, 250 g</t>
         </is>
       </c>
-      <c r="D194" t="n">
-        <v>4</v>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.3 Yogourts et séré nature</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9150,12 +9536,14 @@
           <t>Cheetos XL fromage et paprika, 130 g (retard dans la livraison)</t>
         </is>
       </c>
-      <c r="D195" t="n">
-        <v>7</v>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -9200,12 +9588,14 @@
           <t>Crownfield Granola Honey, au miel, 500 g</t>
         </is>
       </c>
-      <c r="D196" t="n">
-        <v>7</v>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -9250,12 +9640,14 @@
           <t>Fanta, pack de 24, Orange ou Exotic, 24 x 33 cl</t>
         </is>
       </c>
-      <c r="D197" t="n">
-        <v>7</v>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -9284,12 +9676,14 @@
           <t>Coca-Cola, pack de 24, classique ou zéro, 24 x 33 cl</t>
         </is>
       </c>
-      <c r="D198" t="n">
-        <v>7</v>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -9318,12 +9712,14 @@
           <t>Nescafé Dolce Gusto Capsules de café, diverses sortes, 30 pièces</t>
         </is>
       </c>
-      <c r="D199" t="n">
-        <v>1</v>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1. Boissons</t>
+        </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4 Autres</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -9358,12 +9754,14 @@
           <t>Maggi Arôme liquide, 250 g</t>
         </is>
       </c>
-      <c r="D200" t="n">
-        <v>7</v>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6 Sauces et condiments</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -9398,12 +9796,14 @@
           <t>Thomy Mayonnaise / Thomynaise light, 2 x 265 g / 2 x 280 g</t>
         </is>
       </c>
-      <c r="D201" t="n">
-        <v>6</v>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>6. Huiles, matière grasse, graines et oléagineux</t>
+        </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5 Autres</t>
         </is>
       </c>
       <c r="N201" s="2" t="n">
@@ -9427,12 +9827,14 @@
           <t>Thomy Sauce à salades, diverses sortes, 2 x 700 ml</t>
         </is>
       </c>
-      <c r="D202" t="n">
-        <v>7</v>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6 Sauces et condiments</t>
         </is>
       </c>
       <c r="N202" s="2" t="n">
@@ -9456,12 +9858,14 @@
           <t>Nestlé Yogolino, biscuit ou vanille, 4 x 100 g</t>
         </is>
       </c>
-      <c r="D203" t="n">
-        <v>8</v>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>8. Produits pour bébé</t>
+        </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.1 Produits pour bébé</t>
         </is>
       </c>
       <c r="N203" s="2" t="n">
@@ -9485,12 +9889,14 @@
           <t>Nestlé Bouillie au lait, banane-fraises ou banane-pommes, 450 g</t>
         </is>
       </c>
-      <c r="D204" t="n">
-        <v>8</v>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>8. Produits pour bébé</t>
+        </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.1 Produits pour bébé</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -9525,12 +9931,14 @@
           <t>Nestlé Bouillie aux céréales, 8 céréales ou multi-céréales Pyjama, 160 g</t>
         </is>
       </c>
-      <c r="D205" t="n">
-        <v>8</v>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>8. Produits pour bébé</t>
+        </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.1 Produits pour bébé</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -9565,12 +9973,14 @@
           <t>Cailler Tablettes de chocolat, pack de 3, diverses sortes, 600 g</t>
         </is>
       </c>
-      <c r="D206" t="n">
-        <v>7</v>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N206" s="2" t="n">
@@ -9594,12 +10004,14 @@
           <t>Cailler Tablette de chocolat XXL, diverses sortes, 2 kg</t>
         </is>
       </c>
-      <c r="D207" t="n">
-        <v>7</v>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N207" s="2" t="n">
@@ -9623,12 +10035,14 @@
           <t>Cailler Mini branches au lait, 1 kg</t>
         </is>
       </c>
-      <c r="D208" t="n">
-        <v>7</v>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N208" s="2" t="n">
@@ -9652,12 +10066,14 @@
           <t>Cailler Branches, diverses sortes, 690 g</t>
         </is>
       </c>
-      <c r="D209" t="n">
-        <v>7</v>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9686,12 +10102,14 @@
           <t>Bon Gelati Mini Mix amandes, chocolat au lait ou chocolat blanc, surgelés, 12 x 50 ml</t>
         </is>
       </c>
-      <c r="D210" t="n">
-        <v>7</v>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9720,12 +10138,14 @@
           <t>Bon Gelati Bâtonnets glacés fraise croustillante, surgelés, 6 x 100 ml</t>
         </is>
       </c>
-      <c r="D211" t="n">
-        <v>7</v>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9754,12 +10174,14 @@
           <t>Gelatelli Mini glace au café, surgelés, 8 x 38 ml</t>
         </is>
       </c>
-      <c r="D212" t="n">
-        <v>7</v>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9788,12 +10210,14 @@
           <t>Gelatelli Bâtonnets glacés double, diverses sortes, surgelés, 4 x 85 ml / 4 x 90 ml</t>
         </is>
       </c>
-      <c r="D213" t="n">
-        <v>7</v>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9822,12 +10246,14 @@
           <t>Bon Gelati Bâtonnets glacés aux amandes, surgelés, 6 x 100 ml</t>
         </is>
       </c>
-      <c r="D214" t="n">
-        <v>7</v>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9856,12 +10282,14 @@
           <t>Bon Gelati Mini Mix, surgelés, 12 x 50 ml</t>
         </is>
       </c>
-      <c r="D215" t="n">
-        <v>7</v>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9890,12 +10318,14 @@
           <t>Bon Gelati Bâtonnets glacés crisp, vanille, blanc, surgelés, 6 x 120 ml</t>
         </is>
       </c>
-      <c r="D216" t="n">
-        <v>7</v>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -9924,12 +10354,14 @@
           <t>Bon Gelati Bâtonnets glacés vanille, chocolat blanc, amandes, surgelés, 6 x 100 ml</t>
         </is>
       </c>
-      <c r="D217" t="n">
-        <v>7</v>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -9958,12 +10390,14 @@
           <t>Gelatelli Bâtonnets glacés à la pistache, surgelés, 4 x 80 ml</t>
         </is>
       </c>
-      <c r="D218" t="n">
-        <v>7</v>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N218" s="2" t="n">
@@ -9987,12 +10421,14 @@
           <t>Gelatelli Mini Mix fruits, surgelés, 12 x 50 ml</t>
         </is>
       </c>
-      <c r="D219" t="n">
-        <v>7</v>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N219" s="2" t="n">
@@ -10016,12 +10452,14 @@
           <t>Allini Secco, Rosato ou Bianco, 20 cl</t>
         </is>
       </c>
-      <c r="D220" t="n">
-        <v>7</v>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4 Boissons alcoolisées</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -10056,15 +10494,17 @@
           <t>Allini Prosecco DOC, 37,5 cl</t>
         </is>
       </c>
-      <c r="D221" t="n">
-        <v>7</v>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
         <is>
           <t>Italie – Vénétie</t>
         </is>
@@ -10106,12 +10546,14 @@
           <t>Italiamo Escargots pizza, diverses sortes, 270 g</t>
         </is>
       </c>
-      <c r="D222" t="n">
-        <v>7</v>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="N222" s="2" t="n">
@@ -10135,12 +10577,14 @@
           <t>Italiamo Garniture fraîche pour bruschetta, diverses sortes, 150 g</t>
         </is>
       </c>
-      <c r="D223" t="n">
-        <v>7</v>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="N223" s="2" t="n">
@@ -10164,12 +10608,14 @@
           <t>Italiamo Cantuccini à l'orange, 200 g</t>
         </is>
       </c>
-      <c r="D224" t="n">
-        <v>7</v>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N224" s="2" t="n">
@@ -10193,12 +10639,14 @@
           <t>Italiamo Pain en tranches pour bruschetta, 500 g</t>
         </is>
       </c>
-      <c r="D225" t="n">
-        <v>3</v>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1 Pains</t>
         </is>
       </c>
       <c r="N225" s="2" t="n">
@@ -10222,12 +10670,14 @@
           <t>Italiamo Pizza prosciutto mozzarella, surgelée, 400 g</t>
         </is>
       </c>
-      <c r="D226" t="n">
-        <v>7</v>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="N226" s="2" t="n">
@@ -10251,12 +10701,14 @@
           <t>Dr. Oetker Pizza Ristorante, diverses sortes, 355 g – 320 g</t>
         </is>
       </c>
-      <c r="D227" t="n">
-        <v>7</v>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="N227" s="2" t="n">
@@ -10280,12 +10732,14 @@
           <t>Italiamo Pain galette (Piada Sfogliata), 390 g</t>
         </is>
       </c>
-      <c r="D228" t="n">
-        <v>3</v>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>3. Produits céréaliers et pommes de terre</t>
+        </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.1 Pains</t>
         </is>
       </c>
       <c r="N228" s="2" t="n">
@@ -10309,12 +10763,14 @@
           <t>Italiamo Tomates cerises italiennes au jus de tomate, 250 g</t>
         </is>
       </c>
-      <c r="D229" t="n">
-        <v>2</v>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2. Fruits et légumes</t>
+        </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.2 Légumes</t>
         </is>
       </c>
       <c r="N229" s="2" t="n">
@@ -10338,12 +10794,14 @@
           <t>Italiamo Sauces pour pâtes, diverses sortes, 350 g</t>
         </is>
       </c>
-      <c r="D230" t="n">
-        <v>7</v>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.6 Sauces et condiments</t>
         </is>
       </c>
       <c r="N230" s="2" t="n">
@@ -10367,12 +10825,14 @@
           <t>Italiamo Provolone, dolce ou piccante, 300 g</t>
         </is>
       </c>
-      <c r="D231" t="n">
-        <v>4</v>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="N231" s="2" t="n">
@@ -10396,12 +10856,14 @@
           <t>Italiamo Sfogliatine Glassate, 200 g</t>
         </is>
       </c>
-      <c r="D232" t="n">
-        <v>7</v>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -10441,12 +10903,14 @@
           <t>Italiamo Biscuits sablés au lait et au miel, 350 g</t>
         </is>
       </c>
-      <c r="D233" t="n">
-        <v>7</v>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N233" s="2" t="n">
@@ -10470,12 +10934,14 @@
           <t>Italiamo Croissants fourrés à la crème, pistache ou tiramisu, 5 x 48 g</t>
         </is>
       </c>
-      <c r="D234" t="n">
-        <v>7</v>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N234" s="2" t="n">
@@ -10499,12 +10965,14 @@
           <t>Italiamo Gâteau amaretto ou limoncello, surgelé, 700 g / 830 g</t>
         </is>
       </c>
-      <c r="D235" t="n">
-        <v>7</v>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N235" s="2" t="n">
@@ -10528,12 +10996,14 @@
           <t>Gelatelli Lollies Praliné, diverses sortes, surgelés, 4 x 70 ml</t>
         </is>
       </c>
-      <c r="D236" t="n">
-        <v>7</v>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10562,12 +11032,14 @@
           <t>Gelatelli Glace à l'italienne, diverses sortes, surgelée, 500 ml</t>
         </is>
       </c>
-      <c r="D237" t="n">
-        <v>7</v>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N237" s="2" t="n">
@@ -10591,12 +11063,14 @@
           <t>Flaureo Prosecco Rosé Millesimato ou Grillo Spumante Brut, 75 cl</t>
         </is>
       </c>
-      <c r="D238" t="n">
-        <v>7</v>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4 Boissons alcoolisées</t>
         </is>
       </c>
       <c r="N238" s="2" t="n">
@@ -10620,15 +11094,17 @@
           <t>Fantini Farnese Edizione Cinque Autoctoni, 75 cl</t>
         </is>
       </c>
-      <c r="D239" t="n">
-        <v>7</v>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
@@ -10665,15 +11141,17 @@
           <t>Allini Moscato Spumante Dolce, 75 cl</t>
         </is>
       </c>
-      <c r="D240" t="n">
-        <v>7</v>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
@@ -10710,15 +11188,17 @@
           <t>Più Secco, 75 cl</t>
         </is>
       </c>
-      <c r="D241" t="n">
-        <v>7</v>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
@@ -10755,15 +11235,17 @@
           <t>Maestro de Pigo Primitivo di Manduria DOC, 75 cl</t>
         </is>
       </c>
-      <c r="D242" t="n">
-        <v>7</v>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
         <is>
           <t>Italie – Pouilles</t>
         </is>
@@ -10805,12 +11287,14 @@
           <t>Aperol Bitter, 11% vol., 1 l</t>
         </is>
       </c>
-      <c r="D243" t="n">
-        <v>7</v>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4 Boissons alcoolisées</t>
         </is>
       </c>
       <c r="N243" s="2" t="n">
@@ -10834,12 +11318,14 @@
           <t>Aperol Spritz, 9% vol., 3 x 20 cl</t>
         </is>
       </c>
-      <c r="D244" t="n">
-        <v>7</v>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4 Boissons alcoolisées</t>
         </is>
       </c>
       <c r="N244" s="2" t="n">
@@ -10863,15 +11349,17 @@
           <t>Ponte Giulio Orvieto Classico, 75 cl</t>
         </is>
       </c>
-      <c r="D245" t="n">
-        <v>7</v>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
@@ -10897,12 +11385,14 @@
           <t>Duc de Coeur Salami gourmet, diverses sortes, 250 g</t>
         </is>
       </c>
-      <c r="D246" t="n">
-        <v>5</v>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2 Charcuterie</t>
         </is>
       </c>
       <c r="N246" s="2" t="n">
@@ -10926,12 +11416,14 @@
           <t>Duc de Coeur Filet de canard de Barbarie, mariné ou mariné à la provençale, surgelé, 400 g</t>
         </is>
       </c>
-      <c r="D247" t="n">
-        <v>5</v>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>5. Légumineuses, œufs, viande et autres</t>
+        </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.1 Viande hors charcuterie</t>
         </is>
       </c>
       <c r="N247" s="2" t="n">
@@ -10955,12 +11447,14 @@
           <t>Duc de Coeur Coulommiers de Caractère, 350 g</t>
         </is>
       </c>
-      <c r="D248" t="n">
-        <v>4</v>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>4. Produits laitiers</t>
+        </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.1 Fromage</t>
         </is>
       </c>
       <c r="N248" s="2" t="n">
@@ -10984,12 +11478,14 @@
           <t>Duc de Coeur Escargots farcis, surgelés, 67 g</t>
         </is>
       </c>
-      <c r="D249" t="n">
-        <v>7</v>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="N249" s="2" t="n">
@@ -11013,12 +11509,14 @@
           <t>Duc de Coeur Gratin de pommes de terre avec reblochon, surgelé, 360 g</t>
         </is>
       </c>
-      <c r="D250" t="n">
-        <v>7</v>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="N250" s="2" t="n">
@@ -11042,12 +11540,14 @@
           <t>Evian Eau minérale plate, 6 x 1,5 l</t>
         </is>
       </c>
-      <c r="D251" t="n">
-        <v>1</v>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>1. Boissons</t>
+        </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1 Eau nature</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -11082,15 +11582,17 @@
           <t>Côtes du Rhône AOP 2021, 75 cl</t>
         </is>
       </c>
-      <c r="D252" t="n">
-        <v>7</v>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
         <is>
           <t>France – Rhône</t>
         </is>
@@ -11132,12 +11634,14 @@
           <t>Duc de Coeur En-cas au maïs jambon-fromage, 75 g</t>
         </is>
       </c>
-      <c r="D253" t="n">
-        <v>7</v>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="N253" s="2" t="n">
@@ -11161,12 +11665,14 @@
           <t>Duc de Coeur Biscuits au beurre fourrés, diverses sortes, 100 g</t>
         </is>
       </c>
-      <c r="D254" t="n">
-        <v>7</v>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N254" s="2" t="n">
@@ -11190,12 +11696,14 @@
           <t>Duc de Coeur Pâte à tartiner sucrée, diverses sortes, 200 g</t>
         </is>
       </c>
-      <c r="D255" t="n">
-        <v>7</v>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N255" s="2" t="n">
@@ -11219,12 +11727,14 @@
           <t>Duc de Coeur Spécialités de dessert, profiteroles ou crème caramel, 450 g</t>
         </is>
       </c>
-      <c r="D256" t="n">
-        <v>7</v>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N256" s="2" t="n">
@@ -11248,12 +11758,14 @@
           <t>Duc de Coeur Crème brûlée, 2 x 100 g</t>
         </is>
       </c>
-      <c r="D257" t="n">
-        <v>7</v>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="N257" s="2" t="n">
@@ -11277,12 +11789,14 @@
           <t>Duc de Coeur Macarons glacés, surgelés, 6 x 20 g</t>
         </is>
       </c>
-      <c r="D258" t="n">
-        <v>7</v>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1 Sucreries</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11311,15 +11825,17 @@
           <t>Bordeaux Supérieur Barrique AOP 2021, 75 cl</t>
         </is>
       </c>
-      <c r="D259" t="n">
-        <v>7</v>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+        </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
+          <t>7.4 Boissons alcoolisées</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
         <is>
           <t>France – Bordeaux</t>
         </is>

--- a/promotions_extraites.xlsx
+++ b/promotions_extraites.xlsx
@@ -5204,7 +5204,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>7.4 Boissons alcoolisées</t>
+          <t>7.3 Boissons sucrées</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">

--- a/promotions_extraites.xlsx
+++ b/promotions_extraites.xlsx
@@ -1171,12 +1171,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.2 Ingrédients bruts</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.2 Ingrédients bruts</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.2 Ingrédients bruts</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3. Produits céréaliers et pommes de terre</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3.5 Autres</t>
+          <t>10.2 Ingrédients bruts</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3. Produits céréaliers et pommes de terre</t>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3.5 Autres</t>
+          <t>7.5 Plats préparés, pizzas, pâtes farcies, préparations panées</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="N57" s="2" t="n">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5. Légumineuses, œufs, viande et autres</t>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5.3 Poisson</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>5. Légumineuses, œufs, viande et autres</t>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>5.2 Charcuterie</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="N152" s="2" t="n">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>3. Produits céréaliers et pommes de terre</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>3.5 Autres</t>
+          <t>10.2 Ingrédients bruts</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="N286" s="2" t="n">
@@ -19055,12 +19055,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -19102,12 +19102,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -19196,12 +19196,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>4. Produits laitiers</t>
+          <t>9. Compléments alimentaires</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>4.5 Autres</t>
+          <t>9.1 Compléments alimentaires</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -19891,12 +19891,12 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>3. Produits céréaliers et pommes de terre</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.5 Autres</t>
+          <t>10.2 Ingrédients bruts</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -21252,12 +21252,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -29345,12 +29345,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
@@ -29471,12 +29471,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -30164,12 +30164,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
@@ -33519,12 +33519,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
@@ -33592,12 +33592,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="N716" s="2" t="n">
@@ -34559,12 +34559,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
+          <t>10. Condiments et ingrédients</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>7.6 Sauces et condiments</t>
+          <t>10.1 Sauces et condiments</t>
         </is>
       </c>
       <c r="N744" s="2" t="n">

--- a/promotions_extraites.xlsx
+++ b/promotions_extraites.xlsx
@@ -30164,12 +30164,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>10. Condiments et ingrédients</t>
+          <t>7. Boissons sucrées, sucreries, snacks salés, plats préparés et condiments</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>10.1 Sauces et condiments</t>
+          <t>7.2 Snacks salés</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
